--- a/2 Output/Phase1_Baseline_Selected100_Observed/tables/phase1_baseline_executive_results.xlsx
+++ b/2 Output/Phase1_Baseline_Selected100_Observed/tables/phase1_baseline_executive_results.xlsx
@@ -49,14 +49,15 @@
     <sheet name="reint_barriers" sheetId="41" r:id="rId43"/>
     <sheet name="index_correlation_matrix" sheetId="42" r:id="rId44"/>
     <sheet name="readiness_correlations" sheetId="43" r:id="rId45"/>
-    <sheet name="report_ready_figures" sheetId="44" r:id="rId46"/>
+    <sheet name="fig40_operations" sheetId="44" r:id="rId46"/>
+    <sheet name="report_ready_figures" sheetId="45" r:id="rId47"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1599" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1622" uniqueCount="694">
   <si>
     <t>Advancing Justice Uganda - Final Phase 1 Baseline Analysis</t>
   </si>
@@ -76,7 +77,7 @@
     <t>Analysis sample</t>
   </si>
   <si>
-    <t>Primary report: 91 observed interviews from the 100 selected Final Village List LCs; 9 selected units have no matched final survey.</t>
+    <t>Primary report: 93 observed interviews from the 100 selected Final Village List LCs; 7 selected units have no matched final survey.</t>
   </si>
   <si>
     <t>Causal status</t>
@@ -169,7 +170,7 @@
     <t>August 2026 corrective</t>
   </si>
   <si>
-    <t>New / randomly selected</t>
+    <t>New / no documented previous contact</t>
   </si>
   <si>
     <t>Last CDFU phase</t>
@@ -856,7 +857,7 @@
     <t>LCC received reintegration-related case in past 3 months</t>
   </si>
   <si>
-    <t>Any child, SGBV, or other serious/sensitive case in past 3 months</t>
+    <t>Reported child-related or SGBV case in past 3 months</t>
   </si>
   <si>
     <t>Perceived share of cases that are petty/minor and locally handleable, 0-1</t>
@@ -1042,7 +1043,7 @@
     <t>Boundary vignette: correct action/referral</t>
   </si>
   <si>
-    <t>Boundary vignette: correct documentation/procedure</t>
+    <t>Boundary vignette: appropriate actor involvement/notification</t>
   </si>
   <si>
     <t>Family dispute vignette: correct classification</t>
@@ -1051,7 +1052,7 @@
     <t>Family dispute vignette: correct action/referral</t>
   </si>
   <si>
-    <t>Family dispute vignette: correct documentation/procedure</t>
+    <t>Family dispute vignette: appropriate actor involvement/notification</t>
   </si>
   <si>
     <t>Child-related vignette: correct classification</t>
@@ -1060,7 +1061,7 @@
     <t>Child-related vignette: correct action/referral</t>
   </si>
   <si>
-    <t>Child-related vignette: correct documentation/procedure</t>
+    <t>Child-related vignette: appropriate actor involvement/notification</t>
   </si>
   <si>
     <t>SGBV vignette: correct classification</t>
@@ -1069,7 +1070,7 @@
     <t>SGBV vignette: correct action/referral</t>
   </si>
   <si>
-    <t>SGBV vignette: correct documentation/procedure</t>
+    <t>SGBV vignette: appropriate actor involvement/notification</t>
   </si>
   <si>
     <t>ADR and mediation practice</t>
@@ -1114,13 +1115,13 @@
     <t>m5_q16_score</t>
   </si>
   <si>
-    <t>ADR practice score: hearing both sides</t>
-  </si>
-  <si>
-    <t>ADR practice score: neutrality/impartiality</t>
-  </si>
-  <si>
-    <t>ADR practice score: encouraging voluntary agreement</t>
+    <t>Reported frequency of trying ADR before escalation</t>
+  </si>
+  <si>
+    <t>Reported frequency of hearing both sides</t>
+  </si>
+  <si>
+    <t>Reported frequency of allowing uninterrupted explanations</t>
   </si>
   <si>
     <t>ADR practice score: recording agreements</t>
@@ -1309,10 +1310,10 @@
     <t>Referral practice score: receiving feedback</t>
   </si>
   <si>
-    <t>Coordination score with police</t>
-  </si>
-  <si>
-    <t>Coordination score with court/formal justice actors</t>
+    <t>Perceived ease of coordinating with police</t>
+  </si>
+  <si>
+    <t>Perceived ease of coordinating with court/formal justice actors</t>
   </si>
   <si>
     <t>Confidence knowing where to refer cases</t>
@@ -2075,6 +2076,18 @@
   </si>
   <si>
     <t>corr_with_readiness</t>
+  </si>
+  <si>
+    <t>evidence_type</t>
+  </si>
+  <si>
+    <t>Self-reported practice</t>
+  </si>
+  <si>
+    <t>Enumerator-observed</t>
+  </si>
+  <si>
+    <t>Mixed index</t>
   </si>
   <si>
     <t>Figure file</t>
@@ -2242,7 +2255,7 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -2647,31 +2660,31 @@
         <v>153</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.60798011621931092</v>
+        <v>0.61169994950935402</v>
       </c>
       <c r="F2" s="1">
-        <v>0.1495775431394577</v>
+        <v>0.14968527853488922</v>
       </c>
       <c r="G2" s="1">
         <v>0.13571429252624512</v>
       </c>
       <c r="H2" s="1">
-        <v>0.55000001192092896</v>
+        <v>0.55476188659667969</v>
       </c>
       <c r="I2" s="1">
         <v>0.65238094329833984</v>
       </c>
       <c r="J2" s="1">
-        <v>0.70714282989501953</v>
+        <v>0.70952379703521729</v>
       </c>
       <c r="K2" s="1">
         <v>0.83571428060531616</v>
       </c>
       <c r="L2" s="1">
-        <v>0.39201989769935608</v>
+        <v>0.38830006122589111</v>
       </c>
     </row>
     <row r="3">
@@ -2685,13 +2698,13 @@
         <v>154</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.76128336263226937</v>
+        <v>0.76238479569394102</v>
       </c>
       <c r="F3" s="1">
-        <v>0.15502125024795532</v>
+        <v>0.15548752248287201</v>
       </c>
       <c r="G3" s="1">
         <v>0.30000001192092896</v>
@@ -2709,7 +2722,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>0.23871663212776184</v>
+        <v>0.2376151978969574</v>
       </c>
     </row>
     <row r="4">
@@ -2723,19 +2736,19 @@
         <v>155</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.70691392185923818</v>
+        <v>0.70687724249337314</v>
       </c>
       <c r="F4" s="1">
-        <v>0.1329653412103653</v>
+        <v>0.13565343618392944</v>
       </c>
       <c r="G4" s="1">
         <v>0.50555557012557983</v>
       </c>
       <c r="H4" s="1">
-        <v>0.58333331346511841</v>
+        <v>0.58194446563720703</v>
       </c>
       <c r="I4" s="1">
         <v>0.69375002384185791</v>
@@ -2747,7 +2760,7 @@
         <v>0.94930553436279297</v>
       </c>
       <c r="L4" s="1">
-        <v>0.29308608174324036</v>
+        <v>0.29312276840209961</v>
       </c>
     </row>
     <row r="5">
@@ -2761,31 +2774,31 @@
         <v>156</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.65477272647095253</v>
+        <v>0.65486559055505256</v>
       </c>
       <c r="F5" s="1">
-        <v>0.18985609710216522</v>
+        <v>0.18801403045654297</v>
       </c>
       <c r="G5" s="1">
         <v>0.11999999731779099</v>
       </c>
       <c r="H5" s="1">
-        <v>0.53636366128921509</v>
+        <v>0.55909091234207153</v>
       </c>
       <c r="I5" s="1">
         <v>0.68999999761581421</v>
       </c>
       <c r="J5" s="1">
-        <v>0.81818181276321411</v>
+        <v>0.80909091234207153</v>
       </c>
       <c r="K5" s="1">
         <v>0.91818183660507202</v>
       </c>
       <c r="L5" s="1">
-        <v>0.34522727131843567</v>
+        <v>0.34513440728187561</v>
       </c>
     </row>
     <row r="6">
@@ -2799,13 +2812,13 @@
         <v>157</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.615209507205153</v>
       </c>
       <c r="F6" s="1">
-        <v>0.15389686822891235</v>
+        <v>0.15164907276630402</v>
       </c>
       <c r="G6" s="1">
         <v>0.2222222238779068</v>
@@ -2817,13 +2830,13 @@
         <v>0.6111111044883728</v>
       </c>
       <c r="J6" s="1">
-        <v>0.75</v>
+        <v>0.72222220897674561</v>
       </c>
       <c r="K6" s="1">
         <v>0.8928571343421936</v>
       </c>
       <c r="L6" s="1">
-        <v>0.38489121198654175</v>
+        <v>0.38479048013687134</v>
       </c>
     </row>
     <row r="7">
@@ -2837,31 +2850,31 @@
         <v>158</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.52456441365422746</v>
       </c>
       <c r="F7" s="1">
-        <v>0.23968173563480377</v>
+        <v>0.23781652748584747</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>0.4444444477558136</v>
+        <v>0.44696968793869019</v>
       </c>
       <c r="I7" s="1">
         <v>0.60416668653488159</v>
       </c>
       <c r="J7" s="1">
-        <v>0.6736111044883728</v>
+        <v>0.66666668653488159</v>
       </c>
       <c r="K7" s="1">
         <v>0.8611111044883728</v>
       </c>
       <c r="L7" s="1">
-        <v>0.47695615887641907</v>
+        <v>0.47543558478355408</v>
       </c>
     </row>
     <row r="8">
@@ -2875,31 +2888,31 @@
         <v>159</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.74512531829404305</v>
+        <v>0.7479093616367668</v>
       </c>
       <c r="F8" s="1">
-        <v>0.13126222789287567</v>
+        <v>0.1331535279750824</v>
       </c>
       <c r="G8" s="1">
         <v>0.3125</v>
       </c>
       <c r="H8" s="1">
-        <v>0.6524999737739563</v>
+        <v>0.66666668653488159</v>
       </c>
       <c r="I8" s="1">
-        <v>0.76599997282028198</v>
+        <v>0.76800000667572021</v>
       </c>
       <c r="J8" s="1">
-        <v>0.83333331346511841</v>
+        <v>0.83799999952316284</v>
       </c>
       <c r="K8" s="1">
         <v>0.9375</v>
       </c>
       <c r="L8" s="1">
-        <v>0.25487467646598816</v>
+        <v>0.25209063291549683</v>
       </c>
     </row>
     <row r="9">
@@ -2913,13 +2926,13 @@
         <v>160</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.60293040301773571</v>
+        <v>0.60394265286384086</v>
       </c>
       <c r="F9" s="1">
-        <v>0.14762195944786072</v>
+        <v>0.14930187165737152</v>
       </c>
       <c r="G9" s="1">
         <v>0.125</v>
@@ -2937,7 +2950,7 @@
         <v>0.875</v>
       </c>
       <c r="L9" s="1">
-        <v>0.39706960320472717</v>
+        <v>0.39605733752250671</v>
       </c>
     </row>
     <row r="10">
@@ -2951,13 +2964,13 @@
         <v>161</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.69959678268560799</v>
       </c>
       <c r="F10" s="1">
-        <v>0.22323413193225861</v>
+        <v>0.223537877202034</v>
       </c>
       <c r="G10" s="1">
         <v>0.1770833283662796</v>
@@ -2975,7 +2988,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>0.30196884274482727</v>
+        <v>0.30040320754051208</v>
       </c>
     </row>
     <row r="11">
@@ -2989,13 +3002,13 @@
         <v>162</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>0.6187458378928048</v>
+        <v>0.61955237837247956</v>
       </c>
       <c r="F11" s="1">
-        <v>0.11306894570589066</v>
+        <v>0.11352553963661194</v>
       </c>
       <c r="G11" s="1">
         <v>0.28125</v>
@@ -3013,7 +3026,7 @@
         <v>0.83333331346511841</v>
       </c>
       <c r="L11" s="1">
-        <v>0.3812541663646698</v>
+        <v>0.3804476261138916</v>
       </c>
     </row>
     <row r="12">
@@ -3027,31 +3040,31 @@
         <v>163</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.67648417707327957</v>
+        <v>0.67828619063541451</v>
       </c>
       <c r="F12" s="1">
-        <v>0.1300380527973175</v>
+        <v>0.130192831158638</v>
       </c>
       <c r="G12" s="1">
         <v>0.3125</v>
       </c>
       <c r="H12" s="1">
-        <v>0.61458337306976318</v>
+        <v>0.61742424964904785</v>
       </c>
       <c r="I12" s="1">
-        <v>0.72157406806945801</v>
+        <v>0.7181018590927124</v>
       </c>
       <c r="J12" s="1">
-        <v>0.7553703784942627</v>
+        <v>0.75324076414108276</v>
       </c>
       <c r="K12" s="1">
-        <v>0.88194441795349121</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="L12" s="1">
-        <v>0.32351583242416382</v>
+        <v>0.32171380519866943</v>
       </c>
     </row>
     <row r="13">
@@ -3065,13 +3078,13 @@
         <v>164</v>
       </c>
       <c r="D13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
-        <v>0.66870664927985646</v>
+        <v>0.66913728143579221</v>
       </c>
       <c r="F13" s="1">
-        <v>0.11925701797008514</v>
+        <v>0.11961625516414642</v>
       </c>
       <c r="G13" s="1">
         <v>0.40482640266418457</v>
@@ -3089,7 +3102,7 @@
         <v>0.92567867040634155</v>
       </c>
       <c r="L13" s="1">
-        <v>0.33129334449768066</v>
+        <v>0.33086273074150086</v>
       </c>
     </row>
     <row r="14">
@@ -3103,13 +3116,13 @@
         <v>165</v>
       </c>
       <c r="D14" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1">
-        <v>0.61083811914527808</v>
+        <v>0.61174751417611239</v>
       </c>
       <c r="F14" s="1">
-        <v>0.11409930884838104</v>
+        <v>0.11564632505178452</v>
       </c>
       <c r="G14" s="1">
         <v>0.30729168653488159</v>
@@ -3127,7 +3140,7 @@
         <v>0.83333331346511841</v>
       </c>
       <c r="L14" s="1">
-        <v>0.38916188478469849</v>
+        <v>0.38825249671936035</v>
       </c>
     </row>
     <row r="15">
@@ -3141,13 +3154,13 @@
         <v>166</v>
       </c>
       <c r="D15" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1">
-        <v>0.6410022639966273</v>
+        <v>0.64271773253717734</v>
       </c>
       <c r="F15" s="1">
-        <v>0.090111859142780304</v>
+        <v>0.09105180948972702</v>
       </c>
       <c r="G15" s="1">
         <v>0.34234869480133057</v>
@@ -3159,13 +3172,13 @@
         <v>0.64100688695907593</v>
       </c>
       <c r="J15" s="1">
-        <v>0.70569455623626709</v>
+        <v>0.70596063137054443</v>
       </c>
       <c r="K15" s="1">
         <v>0.80475044250488281</v>
       </c>
       <c r="L15" s="1">
-        <v>0.35899773240089417</v>
+        <v>0.35728228092193604</v>
       </c>
     </row>
   </sheetData>
@@ -3202,13 +3215,13 @@
         <v>156</v>
       </c>
       <c r="C2" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1">
-        <v>0.66060227155685425</v>
+        <v>0.65812641382217407</v>
       </c>
       <c r="E2" s="1">
-        <v>0.17607873678207398</v>
+        <v>0.17458510398864746</v>
       </c>
     </row>
     <row r="3">
@@ -3219,13 +3232,13 @@
         <v>164</v>
       </c>
       <c r="C3" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1">
-        <v>0.66633421182632446</v>
+        <v>0.66399264335632324</v>
       </c>
       <c r="E3" s="1">
-        <v>0.11084173619747162</v>
+        <v>0.11046968400478363</v>
       </c>
     </row>
     <row r="4">
@@ -3236,13 +3249,13 @@
         <v>159</v>
       </c>
       <c r="C4" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1">
-        <v>0.76881164312362671</v>
+        <v>0.76343411207199097</v>
       </c>
       <c r="E4" s="1">
-        <v>0.12220512330532074</v>
+        <v>0.12548452615737915</v>
       </c>
     </row>
     <row r="5">
@@ -3253,13 +3266,13 @@
         <v>154</v>
       </c>
       <c r="C5" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1">
-        <v>0.75833332538604736</v>
+        <v>0.76270323991775513</v>
       </c>
       <c r="E5" s="1">
-        <v>0.18011114001274109</v>
+        <v>0.18003323674201965</v>
       </c>
     </row>
     <row r="6">
@@ -3270,13 +3283,13 @@
         <v>155</v>
       </c>
       <c r="C6" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1">
-        <v>0.73284721374511719</v>
+        <v>0.72793024778366089</v>
       </c>
       <c r="E6" s="1">
-        <v>0.12487076222896576</v>
+        <v>0.12725621461868286</v>
       </c>
     </row>
     <row r="7">
@@ -3287,13 +3300,13 @@
         <v>165</v>
       </c>
       <c r="C7" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1">
-        <v>0.60286456346511841</v>
+        <v>0.60010164976119995</v>
       </c>
       <c r="E7" s="1">
-        <v>0.12573650479316712</v>
+        <v>0.12540900707244873</v>
       </c>
     </row>
     <row r="8">
@@ -3304,13 +3317,13 @@
         <v>169</v>
       </c>
       <c r="C8" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1">
-        <v>0.6370542049407959</v>
+        <v>0.63565260171890259</v>
       </c>
       <c r="E8" s="1">
-        <v>0.089492999017238617</v>
+        <v>0.088821835815906525</v>
       </c>
     </row>
     <row r="9">
@@ -3321,13 +3334,13 @@
         <v>163</v>
       </c>
       <c r="C9" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1">
-        <v>0.69354188442230225</v>
+        <v>0.69373100996017456</v>
       </c>
       <c r="E9" s="1">
-        <v>0.12859430909156799</v>
+        <v>0.12698248028755188</v>
       </c>
     </row>
     <row r="10">
@@ -3338,13 +3351,13 @@
         <v>160</v>
       </c>
       <c r="C10" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1">
-        <v>0.60833334922790527</v>
+        <v>0.6046748161315918</v>
       </c>
       <c r="E10" s="1">
-        <v>0.14365744590759277</v>
+        <v>0.14377172291278839</v>
       </c>
     </row>
     <row r="11">
@@ -3355,13 +3368,13 @@
         <v>158</v>
       </c>
       <c r="C11" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1">
-        <v>0.55348062515258789</v>
+        <v>0.55505561828613281</v>
       </c>
       <c r="E11" s="1">
-        <v>0.22597244381904602</v>
+        <v>0.22335769236087799</v>
       </c>
     </row>
     <row r="12">
@@ -3372,13 +3385,13 @@
         <v>157</v>
       </c>
       <c r="C12" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1">
-        <v>0.5878596305847168</v>
+        <v>0.58910423517227173</v>
       </c>
       <c r="E12" s="1">
-        <v>0.13926921784877777</v>
+        <v>0.13774806261062622</v>
       </c>
     </row>
     <row r="13">
@@ -3389,13 +3402,13 @@
         <v>162</v>
       </c>
       <c r="C13" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1">
-        <v>0.59739583730697632</v>
+        <v>0.59552848339080811</v>
       </c>
       <c r="E13" s="1">
-        <v>0.12983761727809906</v>
+        <v>0.12876075506210327</v>
       </c>
     </row>
     <row r="14">
@@ -3406,13 +3419,13 @@
         <v>153</v>
       </c>
       <c r="C14" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1">
-        <v>0.58547616004943848</v>
+        <v>0.5847851037979126</v>
       </c>
       <c r="E14" s="1">
-        <v>0.14951886236667633</v>
+        <v>0.1477043479681015</v>
       </c>
     </row>
     <row r="15">
@@ -3423,13 +3436,13 @@
         <v>161</v>
       </c>
       <c r="C15" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1">
-        <v>0.6840277910232544</v>
+        <v>0.6808096170425415</v>
       </c>
       <c r="E15" s="1">
-        <v>0.20366626977920532</v>
+        <v>0.20215728878974915</v>
       </c>
     </row>
     <row r="16">
@@ -3443,10 +3456,10 @@
         <v>28</v>
       </c>
       <c r="D16" s="1">
-        <v>0.68993508815765381</v>
+        <v>0.69464284181594849</v>
       </c>
       <c r="E16" s="1">
-        <v>0.16421221196651459</v>
+        <v>0.16288197040557861</v>
       </c>
     </row>
     <row r="17">
@@ -3460,10 +3473,10 @@
         <v>28</v>
       </c>
       <c r="D17" s="1">
-        <v>0.67405068874359131</v>
+        <v>0.68068397045135498</v>
       </c>
       <c r="E17" s="1">
-        <v>0.10097047686576843</v>
+        <v>0.10479066520929337</v>
       </c>
     </row>
     <row r="18">
@@ -3477,10 +3490,10 @@
         <v>28</v>
       </c>
       <c r="D18" s="1">
-        <v>0.74998807907104492</v>
+        <v>0.76088094711303711</v>
       </c>
       <c r="E18" s="1">
-        <v>0.099822245538234711</v>
+        <v>0.10228879749774933</v>
       </c>
     </row>
     <row r="19">
@@ -3494,10 +3507,10 @@
         <v>28</v>
       </c>
       <c r="D19" s="1">
-        <v>0.74523806571960449</v>
+        <v>0.73630952835083008</v>
       </c>
       <c r="E19" s="1">
-        <v>0.1334809809923172</v>
+        <v>0.1319652795791626</v>
       </c>
     </row>
     <row r="20">
@@ -3511,10 +3524,10 @@
         <v>28</v>
       </c>
       <c r="D20" s="1">
-        <v>0.66175597906112671</v>
+        <v>0.67328870296478272</v>
       </c>
       <c r="E20" s="1">
-        <v>0.10969697684049606</v>
+        <v>0.12149926275014877</v>
       </c>
     </row>
     <row r="21">
@@ -3528,10 +3541,10 @@
         <v>28</v>
       </c>
       <c r="D21" s="1">
-        <v>0.63915717601776123</v>
+        <v>0.64414232969284058</v>
       </c>
       <c r="E21" s="1">
-        <v>0.074534162878990173</v>
+        <v>0.081902019679546356</v>
       </c>
     </row>
     <row r="22">
@@ -3545,10 +3558,10 @@
         <v>28</v>
       </c>
       <c r="D22" s="1">
-        <v>0.65776664018630981</v>
+        <v>0.66209036111831665</v>
       </c>
       <c r="E22" s="1">
-        <v>0.051219720393419266</v>
+        <v>0.056003138422966003</v>
       </c>
     </row>
     <row r="23">
@@ -3562,10 +3575,10 @@
         <v>28</v>
       </c>
       <c r="D23" s="1">
-        <v>0.66114097833633423</v>
+        <v>0.65865421295166016</v>
       </c>
       <c r="E23" s="1">
-        <v>0.10929124057292938</v>
+        <v>0.10754668712615967</v>
       </c>
     </row>
     <row r="24">
@@ -3579,10 +3592,10 @@
         <v>28</v>
       </c>
       <c r="D24" s="1">
-        <v>0.63809525966644287</v>
+        <v>0.64434522390365601</v>
       </c>
       <c r="E24" s="1">
-        <v>0.098690725862979889</v>
+        <v>0.10787065327167511</v>
       </c>
     </row>
     <row r="25">
@@ -3596,10 +3609,10 @@
         <v>28</v>
       </c>
       <c r="D25" s="1">
-        <v>0.48819670081138611</v>
+        <v>0.47877210378646851</v>
       </c>
       <c r="E25" s="1">
-        <v>0.24518388509750366</v>
+        <v>0.23805494606494904</v>
       </c>
     </row>
     <row r="26">
@@ -3613,10 +3626,10 @@
         <v>28</v>
       </c>
       <c r="D26" s="1">
-        <v>0.67375284433364868</v>
+        <v>0.66842049360275269</v>
       </c>
       <c r="E26" s="1">
-        <v>0.14451070129871369</v>
+        <v>0.14220336079597473</v>
       </c>
     </row>
     <row r="27">
@@ -3630,10 +3643,10 @@
         <v>28</v>
       </c>
       <c r="D27" s="1">
-        <v>0.64021915197372437</v>
+        <v>0.64393937587738037</v>
       </c>
       <c r="E27" s="1">
-        <v>0.076736330986022949</v>
+        <v>0.080498814582824707</v>
       </c>
     </row>
     <row r="28">
@@ -3647,10 +3660,10 @@
         <v>28</v>
       </c>
       <c r="D28" s="1">
-        <v>0.65671771764755249</v>
+        <v>0.66488093137741089</v>
       </c>
       <c r="E28" s="1">
-        <v>0.089779764413833618</v>
+        <v>0.088528238236904144</v>
       </c>
     </row>
     <row r="29">
@@ -3664,10 +3677,10 @@
         <v>28</v>
       </c>
       <c r="D29" s="1">
-        <v>0.67075896263122559</v>
+        <v>0.68638396263122559</v>
       </c>
       <c r="E29" s="1">
-        <v>0.22866156697273254</v>
+        <v>0.23558677732944489</v>
       </c>
     </row>
     <row r="30">
@@ -3678,13 +3691,13 @@
         <v>156</v>
       </c>
       <c r="C30" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D30" s="1">
-        <v>0.60182803869247437</v>
+        <v>0.60288828611373901</v>
       </c>
       <c r="E30" s="1">
-        <v>0.23417282104492188</v>
+        <v>0.22908443212509155</v>
       </c>
     </row>
     <row r="31">
@@ -3695,13 +3708,13 @@
         <v>164</v>
       </c>
       <c r="C31" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D31" s="1">
-        <v>0.66632682085037232</v>
+        <v>0.66445493698120117</v>
       </c>
       <c r="E31" s="1">
-        <v>0.15439479053020477</v>
+        <v>0.15127928555011749</v>
       </c>
     </row>
     <row r="32">
@@ -3712,13 +3725,13 @@
         <v>159</v>
       </c>
       <c r="C32" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D32" s="1">
-        <v>0.69801187515258789</v>
+        <v>0.70625442266464233</v>
       </c>
       <c r="E32" s="1">
-        <v>0.1685570627450943</v>
+        <v>0.16972553730010986</v>
       </c>
     </row>
     <row r="33">
@@ -3729,13 +3742,13 @@
         <v>154</v>
       </c>
       <c r="C33" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D33" s="1">
-        <v>0.78594720363616943</v>
+        <v>0.79226189851760864</v>
       </c>
       <c r="E33" s="1">
-        <v>0.13400653004646301</v>
+        <v>0.13466249406337738</v>
       </c>
     </row>
     <row r="34">
@@ -3746,13 +3759,13 @@
         <v>155</v>
       </c>
       <c r="C34" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D34" s="1">
-        <v>0.71678745746612549</v>
+        <v>0.71009838581085205</v>
       </c>
       <c r="E34" s="1">
-        <v>0.16123388707637787</v>
+        <v>0.16105878353118896</v>
       </c>
     </row>
     <row r="35">
@@ -3763,13 +3776,13 @@
         <v>165</v>
       </c>
       <c r="C35" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D35" s="1">
-        <v>0.59022974967956543</v>
+        <v>0.59384864568710327</v>
       </c>
       <c r="E35" s="1">
-        <v>0.12974464893341064</v>
+        <v>0.12812529504299164</v>
       </c>
     </row>
     <row r="36">
@@ -3780,13 +3793,13 @@
         <v>169</v>
       </c>
       <c r="C36" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D36" s="1">
-        <v>0.62745964527130127</v>
+        <v>0.63218593597412109</v>
       </c>
       <c r="E36" s="1">
-        <v>0.12338373064994812</v>
+        <v>0.12287295609712601</v>
       </c>
     </row>
     <row r="37">
@@ -3797,13 +3810,13 @@
         <v>163</v>
       </c>
       <c r="C37" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D37" s="1">
-        <v>0.66549736261367798</v>
+        <v>0.67480534315109253</v>
       </c>
       <c r="E37" s="1">
-        <v>0.15571783483028412</v>
+        <v>0.15897518396377564</v>
       </c>
     </row>
     <row r="38">
@@ -3814,13 +3827,13 @@
         <v>160</v>
       </c>
       <c r="C38" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D38" s="1">
-        <v>0.55072462558746338</v>
+        <v>0.55555558204650879</v>
       </c>
       <c r="E38" s="1">
-        <v>0.19009421765804291</v>
+        <v>0.18741610646247864</v>
       </c>
     </row>
     <row r="39">
@@ -3831,13 +3844,13 @@
         <v>158</v>
       </c>
       <c r="C39" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D39" s="1">
-        <v>0.51253294944763184</v>
+        <v>0.52589964866638184</v>
       </c>
       <c r="E39" s="1">
-        <v>0.25955164432525635</v>
+        <v>0.26215663552284241</v>
       </c>
     </row>
     <row r="40">
@@ -3848,13 +3861,13 @@
         <v>157</v>
       </c>
       <c r="C40" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D40" s="1">
-        <v>0.59110593795776367</v>
+        <v>0.59772652387619019</v>
       </c>
       <c r="E40" s="1">
-        <v>0.17477826774120331</v>
+        <v>0.17398640513420105</v>
       </c>
     </row>
     <row r="41">
@@ -3865,13 +3878,13 @@
         <v>162</v>
       </c>
       <c r="C41" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D41" s="1">
-        <v>0.62973487377166748</v>
+        <v>0.63214170932769775</v>
       </c>
       <c r="E41" s="1">
-        <v>0.11682321131229401</v>
+        <v>0.11486217379570007</v>
       </c>
     </row>
     <row r="42">
@@ -3882,13 +3895,13 @@
         <v>153</v>
       </c>
       <c r="C42" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D42" s="1">
-        <v>0.58778470754623413</v>
+        <v>0.59563493728637695</v>
       </c>
       <c r="E42" s="1">
-        <v>0.19399523735046387</v>
+        <v>0.19358955323696137</v>
       </c>
     </row>
     <row r="43">
@@ -3899,13 +3912,13 @@
         <v>161</v>
       </c>
       <c r="C43" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D43" s="1">
-        <v>0.75558573007583618</v>
+        <v>0.74710649251937866</v>
       </c>
       <c r="E43" s="1">
-        <v>0.24778220057487488</v>
+        <v>0.24587024748325348</v>
       </c>
     </row>
   </sheetData>
@@ -3939,16 +3952,16 @@
         <v>158</v>
       </c>
       <c r="B2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C2" s="1">
-        <v>0.52304387092590332</v>
+        <v>0.52456438541412354</v>
       </c>
       <c r="D2" s="1">
-        <v>0.23968173563480377</v>
+        <v>0.23781652748584747</v>
       </c>
       <c r="E2" s="1">
-        <v>0.47695612907409668</v>
+        <v>0.47543561458587647</v>
       </c>
     </row>
     <row r="3">
@@ -3956,16 +3969,16 @@
         <v>160</v>
       </c>
       <c r="B3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" s="1">
-        <v>0.60293042659759522</v>
+        <v>0.6039426326751709</v>
       </c>
       <c r="D3" s="1">
-        <v>0.14762195944786072</v>
+        <v>0.14930187165737152</v>
       </c>
       <c r="E3" s="1">
-        <v>0.39706957340240479</v>
+        <v>0.3960573673248291</v>
       </c>
     </row>
     <row r="4">
@@ -3973,16 +3986,16 @@
         <v>153</v>
       </c>
       <c r="B4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" s="1">
-        <v>0.60798013210296631</v>
+        <v>0.61169993877410889</v>
       </c>
       <c r="D4" s="1">
-        <v>0.1495775431394577</v>
+        <v>0.14968527853488922</v>
       </c>
       <c r="E4" s="1">
-        <v>0.39201986789703369</v>
+        <v>0.38830006122589111</v>
       </c>
     </row>
     <row r="5">
@@ -3990,16 +4003,16 @@
         <v>157</v>
       </c>
       <c r="B5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" s="1">
-        <v>0.61510878801345825</v>
+        <v>0.61520951986312866</v>
       </c>
       <c r="D5" s="1">
-        <v>0.15389686822891235</v>
+        <v>0.15164907276630402</v>
       </c>
       <c r="E5" s="1">
-        <v>0.38489121198654175</v>
+        <v>0.38479048013687134</v>
       </c>
     </row>
     <row r="6">
@@ -4007,16 +4020,16 @@
         <v>162</v>
       </c>
       <c r="B6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" s="1">
-        <v>0.61874586343765259</v>
+        <v>0.6195523738861084</v>
       </c>
       <c r="D6" s="1">
-        <v>0.11306894570589066</v>
+        <v>0.11352553963661194</v>
       </c>
       <c r="E6" s="1">
-        <v>0.38125413656234741</v>
+        <v>0.3804476261138916</v>
       </c>
     </row>
     <row r="7">
@@ -4024,16 +4037,16 @@
         <v>156</v>
       </c>
       <c r="B7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" s="1">
-        <v>0.65477269887924194</v>
+        <v>0.654865562915802</v>
       </c>
       <c r="D7" s="1">
-        <v>0.18985609710216522</v>
+        <v>0.18801403045654297</v>
       </c>
       <c r="E7" s="1">
-        <v>0.34522730112075806</v>
+        <v>0.345134437084198</v>
       </c>
     </row>
     <row r="8">
@@ -4041,16 +4054,16 @@
         <v>161</v>
       </c>
       <c r="B8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C8" s="1">
-        <v>0.69803112745285034</v>
+        <v>0.69959676265716553</v>
       </c>
       <c r="D8" s="1">
-        <v>0.22323413193225861</v>
+        <v>0.223537877202034</v>
       </c>
       <c r="E8" s="1">
-        <v>0.30196887254714966</v>
+        <v>0.30040323734283447</v>
       </c>
     </row>
     <row r="9">
@@ -4058,16 +4071,16 @@
         <v>155</v>
       </c>
       <c r="B9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" s="1">
-        <v>0.70691394805908203</v>
+        <v>0.70687723159790039</v>
       </c>
       <c r="D9" s="1">
-        <v>0.1329653412103653</v>
+        <v>0.13565343618392944</v>
       </c>
       <c r="E9" s="1">
-        <v>0.29308605194091797</v>
+        <v>0.29312276840209961</v>
       </c>
     </row>
     <row r="10">
@@ -4075,16 +4088,16 @@
         <v>159</v>
       </c>
       <c r="B10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C10" s="1">
-        <v>0.74512529373168945</v>
+        <v>0.74790936708450317</v>
       </c>
       <c r="D10" s="1">
-        <v>0.13126222789287567</v>
+        <v>0.1331535279750824</v>
       </c>
       <c r="E10" s="1">
-        <v>0.25487470626831055</v>
+        <v>0.25209063291549683</v>
       </c>
     </row>
     <row r="11">
@@ -4092,16 +4105,16 @@
         <v>154</v>
       </c>
       <c r="B11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C11" s="1">
-        <v>0.76128333806991577</v>
+        <v>0.76238477230072022</v>
       </c>
       <c r="D11" s="1">
-        <v>0.15502125024795532</v>
+        <v>0.15548752248287201</v>
       </c>
       <c r="E11" s="1">
-        <v>0.23871666193008423</v>
+        <v>0.23761522769927979</v>
       </c>
     </row>
   </sheetData>
@@ -4159,13 +4172,13 @@
         <v>176</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="F2" s="1">
-        <v>0.45933538675308228</v>
+        <v>0.45637145638465881</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -4194,13 +4207,13 @@
         <v>177</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.25274725274725268</v>
+        <v>0.25806451612903231</v>
       </c>
       <c r="F3" s="1">
-        <v>0.43699496984481812</v>
+        <v>0.43994134664535522</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -4229,13 +4242,13 @@
         <v>178</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.0769230769230769</v>
+        <v>0.086021505376344107</v>
       </c>
       <c r="F4" s="1">
-        <v>0.26794564723968506</v>
+        <v>0.2819155752658844</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -4264,13 +4277,13 @@
         <v>179</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.087912087912087905</v>
+        <v>0.096774193548387094</v>
       </c>
       <c r="F5" s="1">
-        <v>0.2847357988357544</v>
+        <v>0.29725250601768494</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -4364,55 +4377,55 @@
         <v>181</v>
       </c>
       <c r="B2" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1">
-        <v>0.44192546606063843</v>
+        <v>0.44672620296478272</v>
       </c>
       <c r="D2" s="1">
-        <v>0.73614132404327393</v>
+        <v>0.74453127384185791</v>
       </c>
       <c r="E2" s="1">
-        <v>0.6992451548576355</v>
+        <v>0.69224536418914795</v>
       </c>
       <c r="F2" s="1">
-        <v>0.48054346442222595</v>
+        <v>0.48381629586219788</v>
       </c>
       <c r="G2" s="1">
-        <v>0.48739215731620789</v>
+        <v>0.49370452761650086</v>
       </c>
       <c r="H2" s="1">
-        <v>0.38245773315429688</v>
+        <v>0.39227432012557983</v>
       </c>
       <c r="I2" s="1">
-        <v>0.65628963708877564</v>
+        <v>0.65179145336151123</v>
       </c>
       <c r="J2" s="1">
-        <v>0.47282609343528748</v>
+        <v>0.47222223877906799</v>
       </c>
       <c r="K2" s="1">
-        <v>0.61669689416885376</v>
+        <v>0.61400461196899414</v>
       </c>
       <c r="L2" s="1">
-        <v>0.520133376121521</v>
+        <v>0.52016258239746094</v>
       </c>
       <c r="M2" s="1">
-        <v>0.59162956476211548</v>
+        <v>0.59619903564453125</v>
       </c>
       <c r="N2" s="1">
-        <v>0.57096940279006958</v>
+        <v>0.57094269990921021</v>
       </c>
       <c r="O2" s="1">
-        <v>0.49647974967956543</v>
+        <v>0.49619239568710327</v>
       </c>
       <c r="P2" s="1">
-        <v>0.52525103092193604</v>
+        <v>0.52751505374908447</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.043478261679410935</v>
+        <v>0.041666667908430099</v>
       </c>
       <c r="R2" s="1">
-        <v>0.086956523358821869</v>
+        <v>0.083333335816860199</v>
       </c>
       <c r="S2" s="1">
         <v>0</v>
@@ -4491,46 +4504,46 @@
         <v>23</v>
       </c>
       <c r="C4" s="1">
-        <v>0.65900623798370361</v>
+        <v>0.66728776693344116</v>
       </c>
       <c r="D4" s="1">
-        <v>0.78535199165344238</v>
+        <v>0.78278988599777222</v>
       </c>
       <c r="E4" s="1">
-        <v>0.69698065519332886</v>
+        <v>0.69547098875045776</v>
       </c>
       <c r="F4" s="1">
-        <v>0.72648221254348755</v>
+        <v>0.72727274894714355</v>
       </c>
       <c r="G4" s="1">
-        <v>0.6513327956199646</v>
+        <v>0.64891737699508667</v>
       </c>
       <c r="H4" s="1">
-        <v>0.58188772201538086</v>
+        <v>0.58218961954116821</v>
       </c>
       <c r="I4" s="1">
-        <v>0.75956124067306519</v>
+        <v>0.76952505111694336</v>
       </c>
       <c r="J4" s="1">
-        <v>0.63550722599029541</v>
+        <v>0.63224637508392334</v>
       </c>
       <c r="K4" s="1">
-        <v>0.68553745746612549</v>
+        <v>0.68523550033569336</v>
       </c>
       <c r="L4" s="1">
-        <v>0.65081524848937988</v>
+        <v>0.6512681245803833</v>
       </c>
       <c r="M4" s="1">
-        <v>0.70893365144729614</v>
+        <v>0.71150147914886475</v>
       </c>
       <c r="N4" s="1">
-        <v>0.69008326530456543</v>
+        <v>0.68922412395477295</v>
       </c>
       <c r="O4" s="1">
-        <v>0.64316123723983765</v>
+        <v>0.64175724983215332</v>
       </c>
       <c r="P4" s="1">
-        <v>0.67529606819152832</v>
+        <v>0.67744266986846924</v>
       </c>
       <c r="Q4" s="1">
         <v>0.30434781312942505</v>
@@ -4550,61 +4563,61 @@
         <v>184</v>
       </c>
       <c r="B5" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1">
-        <v>0.70616883039474487</v>
+        <v>0.71086955070495605</v>
       </c>
       <c r="D5" s="1">
-        <v>0.78955626487731934</v>
+        <v>0.78768116235733032</v>
       </c>
       <c r="E5" s="1">
-        <v>0.77922981977462769</v>
+        <v>0.78508454561233521</v>
       </c>
       <c r="F5" s="1">
-        <v>0.78512394428253174</v>
+        <v>0.78320157527923584</v>
       </c>
       <c r="G5" s="1">
-        <v>0.73726099729537964</v>
+        <v>0.73373878002166748</v>
       </c>
       <c r="H5" s="1">
-        <v>0.67169421911239624</v>
+        <v>0.6669466495513916</v>
       </c>
       <c r="I5" s="1">
-        <v>0.84229546785354614</v>
+        <v>0.84792029857635498</v>
       </c>
       <c r="J5" s="1">
-        <v>0.72727274894714355</v>
+        <v>0.73550724983215332</v>
       </c>
       <c r="K5" s="1">
-        <v>0.8880997896194458</v>
+        <v>0.892814040184021</v>
       </c>
       <c r="L5" s="1">
-        <v>0.71207815408706665</v>
+        <v>0.71508562564849854</v>
       </c>
       <c r="M5" s="1">
-        <v>0.7678486704826355</v>
+        <v>0.76751601696014404</v>
       </c>
       <c r="N5" s="1">
-        <v>0.79742860794067383</v>
+        <v>0.79870975017547608</v>
       </c>
       <c r="O5" s="1">
-        <v>0.71967542171478272</v>
+        <v>0.72529643774032593</v>
       </c>
       <c r="P5" s="1">
-        <v>0.74778038263320923</v>
+        <v>0.75059795379638672</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.77272725105285645</v>
+        <v>0.73913043737411499</v>
       </c>
       <c r="R5" s="1">
-        <v>0.77272725105285645</v>
+        <v>0.78260868787765503</v>
       </c>
       <c r="S5" s="1">
-        <v>0.27272728085517883</v>
+        <v>0.30434781312942505</v>
       </c>
       <c r="T5" s="1">
-        <v>0.36363637447357178</v>
+        <v>0.39130434393882752</v>
       </c>
     </row>
   </sheetData>
@@ -4635,7 +4648,7 @@
         <v>153</v>
       </c>
       <c r="C2" s="1">
-        <v>0.11616249546337963</v>
+        <v>0.075378305715441934</v>
       </c>
     </row>
     <row r="3">
@@ -4646,7 +4659,7 @@
         <v>154</v>
       </c>
       <c r="C3" s="1">
-        <v>0.64367785785319653</v>
+        <v>0.43769926577613105</v>
       </c>
     </row>
     <row r="4">
@@ -4657,7 +4670,7 @@
         <v>155</v>
       </c>
       <c r="C4" s="1">
-        <v>0.086131924458498002</v>
+        <v>0.25941179010308102</v>
       </c>
     </row>
     <row r="5">
@@ -4668,7 +4681,7 @@
         <v>156</v>
       </c>
       <c r="C5" s="1">
-        <v>0.25058312958992923</v>
+        <v>0.21387383238054281</v>
       </c>
     </row>
     <row r="6">
@@ -4679,7 +4692,7 @@
         <v>157</v>
       </c>
       <c r="C6" s="1">
-        <v>0.051174228196711372</v>
+        <v>0.081681819092074143</v>
       </c>
     </row>
     <row r="7">
@@ -4690,7 +4703,7 @@
         <v>158</v>
       </c>
       <c r="C7" s="1">
-        <v>0.53214718563782881</v>
+        <v>0.42924672580413681</v>
       </c>
     </row>
     <row r="8">
@@ -4701,7 +4714,7 @@
         <v>159</v>
       </c>
       <c r="C8" s="1">
-        <v>0.11577148110128108</v>
+        <v>0.20621855571913658</v>
       </c>
     </row>
     <row r="9">
@@ -4712,7 +4725,7 @@
         <v>160</v>
       </c>
       <c r="C9" s="1">
-        <v>0.10366138165713291</v>
+        <v>0.10087208136012579</v>
       </c>
     </row>
     <row r="10">
@@ -4723,7 +4736,7 @@
         <v>161</v>
       </c>
       <c r="C10" s="1">
-        <v>0.35313066629121481</v>
+        <v>0.48403749842828431</v>
       </c>
     </row>
     <row r="11">
@@ -4734,7 +4747,7 @@
         <v>162</v>
       </c>
       <c r="C11" s="1">
-        <v>0.26802626941838892</v>
+        <v>0.18152318574134302</v>
       </c>
     </row>
     <row r="12">
@@ -4745,7 +4758,7 @@
         <v>163</v>
       </c>
       <c r="C12" s="1">
-        <v>0.54250448755918424</v>
+        <v>0.54547619556210214</v>
       </c>
     </row>
     <row r="13">
@@ -4756,7 +4769,7 @@
         <v>164</v>
       </c>
       <c r="C13" s="1">
-        <v>0.96105600142690995</v>
+        <v>0.83270379422512342</v>
       </c>
     </row>
     <row r="14">
@@ -4767,7 +4780,7 @@
         <v>165</v>
       </c>
       <c r="C14" s="1">
-        <v>0.26571118500096974</v>
+        <v>0.20456143150042688</v>
       </c>
     </row>
     <row r="15">
@@ -4778,7 +4791,7 @@
         <v>166</v>
       </c>
       <c r="C15" s="1">
-        <v>0.46207783472712327</v>
+        <v>0.40378661884465178</v>
       </c>
     </row>
   </sheetData>
@@ -4836,13 +4849,13 @@
         <v>40</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.1098901098901099</v>
+        <v>0.1075268817204301</v>
       </c>
       <c r="F2" s="1">
-        <v>0.31448546051979065</v>
+        <v>0.31146100163459778</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -4871,13 +4884,13 @@
         <v>41</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.14285714285714279</v>
+        <v>0.15053763440860221</v>
       </c>
       <c r="F3" s="1">
-        <v>0.35186576843261719</v>
+        <v>0.35953584313392639</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -4906,13 +4919,13 @@
         <v>42</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.38827838827838829</v>
+        <v>0.3942652329749104</v>
       </c>
       <c r="F4" s="1">
-        <v>0.21809351444244385</v>
+        <v>0.22086915373802185</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -4941,25 +4954,25 @@
         <v>43</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>16.428571428571431</v>
+        <v>16.473118279569889</v>
       </c>
       <c r="F5" s="1">
-        <v>11.821020126342773</v>
+        <v>11.662454605102539</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="1">
         <v>15</v>
       </c>
       <c r="J5" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K5" s="1">
         <v>41</v>
@@ -4976,19 +4989,19 @@
         <v>204</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.79340659340659348</v>
+        <v>0.80215053763440858</v>
       </c>
       <c r="F6" s="1">
-        <v>0.3292422890663147</v>
+        <v>0.32703492045402527</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>0.69999998807907105</v>
+        <v>0.80000001192092896</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -5011,13 +5024,13 @@
         <v>205</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.65384615384615386</v>
+        <v>0.65591397849462363</v>
       </c>
       <c r="F7" s="1">
-        <v>0.18169429898262024</v>
+        <v>0.18025487661361694</v>
       </c>
       <c r="G7" s="1">
         <v>0.25</v>
@@ -5046,13 +5059,13 @@
         <v>206</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.26373626373626369</v>
+        <v>0.27956989247311831</v>
       </c>
       <c r="F8" s="1">
-        <v>0.44309931993484497</v>
+        <v>0.45122036337852478</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -5081,13 +5094,13 @@
         <v>207</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.97802197802197799</v>
+        <v>0.978494623655914</v>
       </c>
       <c r="F9" s="1">
-        <v>0.14742395281791687</v>
+        <v>0.14584794640541077</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -5116,7 +5129,7 @@
         <v>208</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -5151,13 +5164,13 @@
         <v>44</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>0.68131868131868134</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F11" s="1">
-        <v>0.46854671835899353</v>
+        <v>0.46575078368186951</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -5186,13 +5199,13 @@
         <v>45</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.87912087912087911</v>
+        <v>0.88172043010752688</v>
       </c>
       <c r="F12" s="1">
-        <v>0.32779279351234436</v>
+        <v>0.32468923926353455</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -5221,13 +5234,13 @@
         <v>46</v>
       </c>
       <c r="D13" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E13" s="1">
-        <v>0.17241379310344829</v>
+        <v>0.1797752808988764</v>
       </c>
       <c r="F13" s="1">
-        <v>0.37992951273918152</v>
+        <v>0.38617581129074097</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -5256,13 +5269,13 @@
         <v>209</v>
       </c>
       <c r="D14" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E14" s="1">
-        <v>2.333333333333333</v>
+        <v>2.3125</v>
       </c>
       <c r="F14" s="1">
-        <v>1.1126972436904907</v>
+        <v>1.078192949295044</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -5271,7 +5284,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J14" s="1">
         <v>3</v>
@@ -5291,13 +5304,13 @@
         <v>210</v>
       </c>
       <c r="D15" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1">
-        <v>0.61538461538461542</v>
+        <v>0.61505376344086027</v>
       </c>
       <c r="F15" s="1">
-        <v>0.25338730216026306</v>
+        <v>0.2540738582611084</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -5326,13 +5339,13 @@
         <v>211</v>
       </c>
       <c r="D16" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1">
-        <v>0.1318681318681319</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="F16" s="1">
-        <v>0.34022185206413269</v>
+        <v>0.33705264329910278</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -5361,13 +5374,13 @@
         <v>212</v>
       </c>
       <c r="D17" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E17" s="1">
-        <v>0.2445054945054945</v>
+        <v>0.2446236559139785</v>
       </c>
       <c r="F17" s="1">
-        <v>0.12347976863384247</v>
+        <v>0.12213285267353058</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -5396,25 +5409,25 @@
         <v>153</v>
       </c>
       <c r="D18" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E18" s="1">
-        <v>0.60798011621931092</v>
+        <v>0.61169994950935402</v>
       </c>
       <c r="F18" s="1">
-        <v>0.1495775431394577</v>
+        <v>0.14968527853488922</v>
       </c>
       <c r="G18" s="1">
         <v>0.13571429252624512</v>
       </c>
       <c r="H18" s="1">
-        <v>0.55000001192092896</v>
+        <v>0.55476188659667969</v>
       </c>
       <c r="I18" s="1">
         <v>0.65238094329833984</v>
       </c>
       <c r="J18" s="1">
-        <v>0.70714282989501953</v>
+        <v>0.70952379703521729</v>
       </c>
       <c r="K18" s="1">
         <v>0.83571428060531616</v>
@@ -5493,58 +5506,58 @@
         <v>32</v>
       </c>
       <c r="B2" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1">
-        <v>0.125</v>
+        <v>0.12195122241973877</v>
       </c>
       <c r="D2" s="1">
-        <v>0.15000000596046448</v>
+        <v>0.14634145796298981</v>
       </c>
       <c r="E2" s="1">
-        <v>0.43333333333333346</v>
+        <v>0.43495934959349608</v>
       </c>
       <c r="F2" s="1">
-        <v>14.699999999999999</v>
+        <v>14.780487804878049</v>
       </c>
       <c r="G2" s="1">
-        <v>0.74750000000000016</v>
+        <v>0.75365853658536586</v>
       </c>
       <c r="H2" s="1">
-        <v>0.60624999999999996</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="I2" s="1">
-        <v>0.375</v>
+        <v>0.39024388790130615</v>
       </c>
       <c r="J2" s="1">
-        <v>0.94999998807907105</v>
+        <v>0.95121949911117554</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>0.57499998807907104</v>
+        <v>0.56097561120986938</v>
       </c>
       <c r="M2" s="1">
-        <v>0.875</v>
+        <v>0.87804877758026123</v>
       </c>
       <c r="N2" s="1">
-        <v>0.28205129504203796</v>
+        <v>0.27500000596046448</v>
       </c>
       <c r="O2" s="1">
         <v>2.4545454978942871</v>
       </c>
       <c r="P2" s="1">
-        <v>0.60499999999999998</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.125</v>
+        <v>0.12195122241973877</v>
       </c>
       <c r="R2" s="1">
-        <v>0.25624999999999998</v>
+        <v>0.25609756097560976</v>
       </c>
       <c r="S2" s="1">
-        <v>0.58547616004943848</v>
+        <v>0.5847851037979126</v>
       </c>
     </row>
     <row r="3">
@@ -5564,10 +5577,10 @@
         <v>0.30952380952380948</v>
       </c>
       <c r="F3" s="1">
-        <v>22.25</v>
+        <v>22.392857142857142</v>
       </c>
       <c r="G3" s="1">
-        <v>0.91785714285714293</v>
+        <v>0.93214285714285705</v>
       </c>
       <c r="H3" s="1">
         <v>0.6696428571428571</v>
@@ -5582,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>0.8571428656578064</v>
+        <v>0.8928571343421936</v>
       </c>
       <c r="M3" s="1">
         <v>0.96428573131561279</v>
@@ -5594,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="P3" s="1">
-        <v>0.62857142857142845</v>
+        <v>0.63571428571428557</v>
       </c>
       <c r="Q3" s="1">
         <v>0.1071428582072258</v>
@@ -5603,7 +5616,7 @@
         <v>0.25</v>
       </c>
       <c r="S3" s="1">
-        <v>0.65671771764755249</v>
+        <v>0.66488093137741089</v>
       </c>
     </row>
     <row r="4">
@@ -5611,56 +5624,58 @@
         <v>34</v>
       </c>
       <c r="B4" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
+        <v>0.041666667908430099</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="F4" s="1">
+        <v>12.458333333333334</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.73333333333333339</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.71875</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.3333333432674408</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.66666668653488159</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.79166668653488159</v>
+      </c>
+      <c r="N4" s="1">
         <v>0.043478261679410935</v>
       </c>
-      <c r="D4" s="1">
-        <v>0.21739129722118378</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.40579710144927533</v>
-      </c>
-      <c r="F4" s="1">
-        <v>12.347826086956522</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.72173913043478266</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0.71739130434782605</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.30434781312942505</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0.65217393636703491</v>
-      </c>
-      <c r="M4" s="1">
-        <v>0.78260868787765503</v>
-      </c>
-      <c r="N4" s="1">
-        <v>0</v>
-      </c>
-      <c r="O4" s="1"/>
+      <c r="O4" s="1">
+        <v>2</v>
+      </c>
       <c r="P4" s="1">
-        <v>0.61739130434782619</v>
+        <v>0.61666666666666659</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.17391304671764374</v>
+        <v>0.1666666716337204</v>
       </c>
       <c r="R4" s="1">
-        <v>0.21739130434782608</v>
+        <v>0.21875</v>
       </c>
       <c r="S4" s="1">
-        <v>0.58778470754623413</v>
+        <v>0.59563493728637695</v>
       </c>
     </row>
   </sheetData>
@@ -5718,19 +5733,19 @@
         <v>228</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>8.5934065934065931</v>
+        <v>8.612903225806452</v>
       </c>
       <c r="F2" s="1">
-        <v>2.3663287162780762</v>
+        <v>2.3684165477752686</v>
       </c>
       <c r="G2" s="1">
         <v>5</v>
       </c>
       <c r="H2" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2" s="1">
         <v>9</v>
@@ -5753,13 +5768,13 @@
         <v>229</v>
       </c>
       <c r="D3" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" s="1">
-        <v>2.9888888888888889</v>
+        <v>3.0217391304347832</v>
       </c>
       <c r="F3" s="1">
-        <v>1.075722336769104</v>
+        <v>1.0790538787841797</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
@@ -5788,13 +5803,13 @@
         <v>230</v>
       </c>
       <c r="D4" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" s="1">
-        <v>0.36216209716209708</v>
+        <v>0.36467861848296629</v>
       </c>
       <c r="F4" s="1">
-        <v>0.11784441024065018</v>
+        <v>0.1162620410323143</v>
       </c>
       <c r="G4" s="1">
         <v>0.090909093618392944</v>
@@ -5803,7 +5818,7 @@
         <v>0.27272728085517883</v>
       </c>
       <c r="I4" s="1">
-        <v>0.36931818723678589</v>
+        <v>0.375</v>
       </c>
       <c r="J4" s="1">
         <v>0.4285714328289032</v>
@@ -5823,7 +5838,7 @@
         <v>231</v>
       </c>
       <c r="D5" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -5858,13 +5873,13 @@
         <v>232</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.49450549450549453</v>
+        <v>0.4946236559139785</v>
       </c>
       <c r="F6" s="1">
-        <v>0.50273972749710083</v>
+        <v>0.5026809573173523</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -5893,13 +5908,13 @@
         <v>233</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>3.9890109890109891</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1">
-        <v>5.7783012390136719</v>
+        <v>5.719912052154541</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -5928,13 +5943,13 @@
         <v>234</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.61098901098901104</v>
+        <v>0.61397849462365595</v>
       </c>
       <c r="F8" s="1">
-        <v>0.21676948666572571</v>
+        <v>0.21848858892917633</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -5963,13 +5978,13 @@
         <v>235</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.85164835164835162</v>
+        <v>0.85483870967741937</v>
       </c>
       <c r="F9" s="1">
-        <v>0.23856638371944428</v>
+        <v>0.23694896697998047</v>
       </c>
       <c r="G9" s="1">
         <v>0.25</v>
@@ -5998,13 +6013,13 @@
         <v>236</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.92307692307692313</v>
+        <v>0.92473118279569888</v>
       </c>
       <c r="F10" s="1">
-        <v>0.20980250835418701</v>
+        <v>0.20781257748603821</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -6033,13 +6048,13 @@
         <v>237</v>
       </c>
       <c r="D11" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E11" s="1">
-        <v>0.76666666666666672</v>
+        <v>0.76630434782608692</v>
       </c>
       <c r="F11" s="1">
-        <v>0.30168068408966065</v>
+        <v>0.30065026879310608</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -6068,13 +6083,13 @@
         <v>238</v>
       </c>
       <c r="D12" s="1">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E12" s="1">
-        <v>0.79411764705882348</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="F12" s="1">
-        <v>0.32084447145462036</v>
+        <v>0.3194446861743927</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -6103,13 +6118,13 @@
         <v>239</v>
       </c>
       <c r="D13" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E13" s="1">
-        <v>0.64880952380952384</v>
+        <v>0.65116279069767447</v>
       </c>
       <c r="F13" s="1">
-        <v>0.28811562061309814</v>
+        <v>0.28768616914749146</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -6138,13 +6153,13 @@
         <v>240</v>
       </c>
       <c r="D14" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1">
-        <v>1.8241758241758239</v>
+        <v>1.827956989247312</v>
       </c>
       <c r="F14" s="1">
-        <v>1.7925363779067993</v>
+        <v>1.7974840402603149</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -6173,13 +6188,13 @@
         <v>241</v>
       </c>
       <c r="D15" s="1">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E15" s="1">
-        <v>0.72666666666666668</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="F15" s="1">
-        <v>0.34182867407798767</v>
+        <v>0.33975082635879517</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -6208,13 +6223,13 @@
         <v>242</v>
       </c>
       <c r="D16" s="1">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E16" s="1">
-        <v>0.86764705882352944</v>
+        <v>0.86428571428571432</v>
       </c>
       <c r="F16" s="1">
-        <v>0.28148919343948364</v>
+        <v>0.28131973743438721</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -6243,13 +6258,13 @@
         <v>154</v>
       </c>
       <c r="D17" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E17" s="1">
-        <v>0.76128336263226937</v>
+        <v>0.76238479569394102</v>
       </c>
       <c r="F17" s="1">
-        <v>0.15502125024795532</v>
+        <v>0.15548752248287201</v>
       </c>
       <c r="G17" s="1">
         <v>0.30000001192092896</v>
@@ -6321,7 +6336,7 @@
         <v>48</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
         <v>100</v>
@@ -6338,7 +6353,7 @@
         <v>48</v>
       </c>
       <c r="D4" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1">
         <v>100</v>
@@ -6355,10 +6370,10 @@
         <v>48</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -6372,10 +6387,10 @@
         <v>48</v>
       </c>
       <c r="D6" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -6389,10 +6404,10 @@
         <v>49</v>
       </c>
       <c r="D7" s="1">
-        <v>43.956043956043956</v>
+        <v>44.086021505376344</v>
       </c>
       <c r="E7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
@@ -6409,7 +6424,7 @@
         <v>28</v>
       </c>
       <c r="E8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
@@ -6423,10 +6438,10 @@
         <v>49</v>
       </c>
       <c r="D9" s="1">
-        <v>30.76923076923077</v>
+        <v>30.107526881720432</v>
       </c>
       <c r="E9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -6440,10 +6455,10 @@
         <v>48</v>
       </c>
       <c r="D10" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -6457,10 +6472,10 @@
         <v>49</v>
       </c>
       <c r="D11" s="1">
-        <v>25.274725274725274</v>
+        <v>25.806451612903224</v>
       </c>
       <c r="E11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -6474,10 +6489,10 @@
         <v>48</v>
       </c>
       <c r="D12" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -6491,10 +6506,10 @@
         <v>48</v>
       </c>
       <c r="D13" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -6508,10 +6523,10 @@
         <v>48</v>
       </c>
       <c r="D14" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -6528,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
@@ -6545,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6559,10 +6574,10 @@
         <v>50</v>
       </c>
       <c r="D17" s="1">
-        <v>0.10989010989010989</v>
+        <v>0.10752688172043011</v>
       </c>
       <c r="E17" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
@@ -6576,10 +6591,10 @@
         <v>50</v>
       </c>
       <c r="D18" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.15053763440860216</v>
       </c>
       <c r="E18" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -6593,10 +6608,10 @@
         <v>50</v>
       </c>
       <c r="D19" s="1">
-        <v>0.38827838827838829</v>
+        <v>0.3942652329749104</v>
       </c>
       <c r="E19" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -6610,10 +6625,10 @@
         <v>50</v>
       </c>
       <c r="D20" s="1">
-        <v>16.428571428571427</v>
+        <v>16.473118279569892</v>
       </c>
       <c r="E20" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
@@ -6627,10 +6642,10 @@
         <v>50</v>
       </c>
       <c r="D21" s="1">
-        <v>0.68131868131868134</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="E21" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22">
@@ -6644,10 +6659,10 @@
         <v>50</v>
       </c>
       <c r="D22" s="1">
-        <v>0.87912087912087911</v>
+        <v>0.88172043010752688</v>
       </c>
       <c r="E22" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23">
@@ -6661,10 +6676,10 @@
         <v>50</v>
       </c>
       <c r="D23" s="1">
-        <v>0.17241379310344829</v>
+        <v>0.1797752808988764</v>
       </c>
       <c r="E23" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -6740,56 +6755,56 @@
         <v>32</v>
       </c>
       <c r="B2" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1">
-        <v>8.5999999999999997</v>
+        <v>8.6585365853658534</v>
       </c>
       <c r="D2" s="1">
-        <v>3.2250000000000001</v>
+        <v>3.2195121951219514</v>
       </c>
       <c r="E2" s="1">
-        <v>0.38580898268398278</v>
+        <v>0.38305089219723376</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0.44999998807907104</v>
+        <v>0.46341463923454285</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1">
-        <v>4.5750000000000002</v>
+        <v>4.6097560975609753</v>
       </c>
       <c r="J2" s="1">
-        <v>0.59000000000000008</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="K2" s="1">
-        <v>0.84999999999999998</v>
+        <v>0.85365853658536584</v>
       </c>
       <c r="L2" s="1">
-        <v>0.91249999999999998</v>
+        <v>0.91463414634146345</v>
       </c>
       <c r="M2" s="1">
-        <v>0.82051282051282048</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="N2" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.83750000000000002</v>
       </c>
       <c r="O2" s="1">
-        <v>0.57894736842105266</v>
+        <v>0.57692307692307687</v>
       </c>
       <c r="P2" s="1">
-        <v>2.0499999523162842</v>
+        <v>2.0731706619262695</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.70833333333333337</v>
+        <v>0.71621621621621623</v>
       </c>
       <c r="R2" s="1">
-        <v>0.90322580645161288</v>
+        <v>0.90625</v>
       </c>
       <c r="S2" s="1">
-        <v>0.75833332538604736</v>
+        <v>0.76270323991775513</v>
       </c>
     </row>
     <row r="3">
@@ -6800,26 +6815,26 @@
         <v>28</v>
       </c>
       <c r="C3" s="1">
-        <v>8.5714285714285712</v>
+        <v>8.4642857142857135</v>
       </c>
       <c r="D3" s="1">
-        <v>2.5925925925925926</v>
+        <v>2.6296296296296298</v>
       </c>
       <c r="E3" s="1">
-        <v>0.32320025653358991</v>
+        <v>0.33166586499919837</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0.6071428656578064</v>
+        <v>0.57142859697341919</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1">
         <v>4.7142857142857144</v>
       </c>
       <c r="J3" s="1">
-        <v>0.62857142857142867</v>
+        <v>0.62857142857142845</v>
       </c>
       <c r="K3" s="1">
         <v>0.8392857142857143</v>
@@ -6828,25 +6843,25 @@
         <v>0.89285714285714291</v>
       </c>
       <c r="M3" s="1">
-        <v>0.75</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="N3" s="1">
-        <v>0.67307692307692313</v>
+        <v>0.65384615384615386</v>
       </c>
       <c r="O3" s="1">
         <v>0.71153846153846157</v>
       </c>
       <c r="P3" s="1">
-        <v>1.7142857313156128</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.73684210526315785</v>
+        <v>0.71052631578947367</v>
       </c>
       <c r="R3" s="1">
-        <v>0.77777777777777779</v>
+        <v>0.75</v>
       </c>
       <c r="S3" s="1">
-        <v>0.74523806571960449</v>
+        <v>0.73630952835083008</v>
       </c>
     </row>
     <row r="4">
@@ -6854,56 +6869,56 @@
         <v>34</v>
       </c>
       <c r="B4" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
-        <v>8.6086956521739122</v>
+        <v>8.7083333333333339</v>
       </c>
       <c r="D4" s="1">
-        <v>3.0434782608695654</v>
+        <v>3.125</v>
       </c>
       <c r="E4" s="1">
-        <v>0.3667748917748917</v>
+        <v>0.37043199855699854</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0.43478259444236755</v>
+        <v>0.4583333432674408</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1">
-        <v>2.0869565217391304</v>
+        <v>2.125</v>
       </c>
       <c r="J4" s="1">
-        <v>0.62608695652173907</v>
+        <v>0.62083333333333324</v>
       </c>
       <c r="K4" s="1">
-        <v>0.86956521739130432</v>
+        <v>0.875</v>
       </c>
       <c r="L4" s="1">
-        <v>0.97826086956521741</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="M4" s="1">
-        <v>0.69565217391304346</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="N4" s="1">
-        <v>0.875</v>
+        <v>0.88095238095238093</v>
       </c>
       <c r="O4" s="1">
-        <v>0.69999999999999996</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="P4" s="1">
-        <v>1.5652173757553101</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.75</v>
+        <v>0.76190476190476186</v>
       </c>
       <c r="R4" s="1">
-        <v>0.89473684210526316</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="S4" s="1">
-        <v>0.78594720363616943</v>
+        <v>0.79226189851760864</v>
       </c>
     </row>
   </sheetData>
@@ -6961,13 +6976,13 @@
         <v>257</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.87912087912087911</v>
+        <v>0.89247311827956988</v>
       </c>
       <c r="F2" s="1">
-        <v>1.4050319194793701</v>
+        <v>1.4023455381393433</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -6996,13 +7011,13 @@
         <v>258</v>
       </c>
       <c r="D3" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" s="1">
-        <v>1.966292134831461</v>
+        <v>2.0109890109890109</v>
       </c>
       <c r="F3" s="1">
-        <v>2.5648384094238281</v>
+        <v>2.5755021572113037</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -7031,13 +7046,13 @@
         <v>259</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.24175824175824179</v>
+        <v>0.23655913978494619</v>
       </c>
       <c r="F4" s="1">
-        <v>0.56451869010925293</v>
+        <v>0.55946111679077148</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -7066,13 +7081,13 @@
         <v>260</v>
       </c>
       <c r="D5" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E5" s="1">
-        <v>0.079722222222222194</v>
+        <v>0.0771505376344086</v>
       </c>
       <c r="F5" s="1">
-        <v>0.20961114764213562</v>
+        <v>0.20663480460643768</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -7101,13 +7116,13 @@
         <v>261</v>
       </c>
       <c r="D6" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1">
-        <v>0.20634920634920631</v>
+        <v>0.2153846153846154</v>
       </c>
       <c r="F6" s="1">
-        <v>0.54354661703109741</v>
+        <v>0.54464173316955566</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -7136,13 +7151,13 @@
         <v>262</v>
       </c>
       <c r="D7" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E7" s="1">
-        <v>0.11375661375661381</v>
+        <v>0.1153846153846154</v>
       </c>
       <c r="F7" s="1">
-        <v>0.29455238580703735</v>
+        <v>0.29155218601226807</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -7174,10 +7189,10 @@
         <v>91</v>
       </c>
       <c r="E8" s="1">
-        <v>1.9230769230769229</v>
+        <v>2.0109890109890109</v>
       </c>
       <c r="F8" s="1">
-        <v>1.6880676746368408</v>
+        <v>1.7159028053283692</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -7241,7 +7256,7 @@
         <v>265</v>
       </c>
       <c r="D10" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -7311,13 +7326,13 @@
         <v>267</v>
       </c>
       <c r="D12" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E12" s="1">
-        <v>0.53015873015873016</v>
+        <v>0.53230769230769237</v>
       </c>
       <c r="F12" s="1">
-        <v>0.35769644379615784</v>
+        <v>0.35929954051971436</v>
       </c>
       <c r="G12" s="1">
         <v>0.20000000298023224</v>
@@ -7346,13 +7361,13 @@
         <v>268</v>
       </c>
       <c r="D13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
-        <v>0.67307692307692313</v>
+        <v>0.67473118279569888</v>
       </c>
       <c r="F13" s="1">
-        <v>0.18518874049186707</v>
+        <v>0.18350803852081299</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -7431,28 +7446,28 @@
         <v>32</v>
       </c>
       <c r="B2" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1">
-        <v>0.94999999999999996</v>
+        <v>0.97560975609756095</v>
       </c>
       <c r="D2" s="1">
-        <v>1.9487179487179487</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="E2" s="1">
-        <v>0.20000000000000001</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="F2" s="1">
-        <v>0.10432098765432098</v>
+        <v>0.1005952380952381</v>
       </c>
       <c r="G2" s="1">
-        <v>0.22222222222222221</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="H2" s="1">
-        <v>0.13580246913580246</v>
+        <v>0.13095238095238096</v>
       </c>
       <c r="I2" s="1">
-        <v>2</v>
+        <v>2.0499999523162842</v>
       </c>
       <c r="J2" s="1">
         <v>0.075000002980232239</v>
@@ -7464,10 +7479,10 @@
         <v>0.075000002980232239</v>
       </c>
       <c r="M2" s="1">
-        <v>0.54814814814814816</v>
+        <v>0.56428571428571417</v>
       </c>
       <c r="N2" s="1">
-        <v>0.68125000000000002</v>
+        <v>0.68292682926829274</v>
       </c>
       <c r="O2" s="1">
         <v>1</v>
@@ -7481,10 +7496,10 @@
         <v>27</v>
       </c>
       <c r="C3" s="1">
-        <v>0.89285714285714291</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D3" s="1">
-        <v>2.3703703703703702</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="E3" s="1">
         <v>0.2857142857142857</v>
@@ -7499,19 +7514,19 @@
         <v>0.13157894736842105</v>
       </c>
       <c r="I3" s="1">
-        <v>2</v>
+        <v>2.2222223281860352</v>
       </c>
       <c r="J3" s="1">
-        <v>0.035714287310838699</v>
+        <v>0.037037037312984467</v>
       </c>
       <c r="K3" s="1">
         <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>0.035714287310838699</v>
+        <v>0.037037037312984467</v>
       </c>
       <c r="M3" s="1">
-        <v>0.59999999999999998</v>
+        <v>0.55789473684210533</v>
       </c>
       <c r="N3" s="1">
         <v>0.6875</v>
@@ -7525,28 +7540,28 @@
         <v>34</v>
       </c>
       <c r="B4" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
-        <v>0.73913043478260865</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D4" s="1">
-        <v>1.5217391304347827</v>
+        <v>1.5833333333333333</v>
       </c>
       <c r="E4" s="1">
-        <v>0.2608695652173913</v>
+        <v>0.25</v>
       </c>
       <c r="F4" s="1">
-        <v>0.066666666666666666</v>
+        <v>0.0625</v>
       </c>
       <c r="G4" s="1">
-        <v>0.11764705882352941</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="H4" s="1">
-        <v>0.058823529411764705</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="I4" s="1">
-        <v>1.6956521272659302</v>
+        <v>1.7083333730697632</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
@@ -7558,10 +7573,10 @@
         <v>0</v>
       </c>
       <c r="M4" s="1">
-        <v>0.42352941176470588</v>
+        <v>0.45555555555555549</v>
       </c>
       <c r="N4" s="1">
-        <v>0.64130434782608692</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="O4" s="1">
         <v>1</v>
@@ -7636,13 +7651,13 @@
         <v>282</v>
       </c>
       <c r="D2" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" s="1">
-        <v>0.69841269841269837</v>
+        <v>0.70769230769230773</v>
       </c>
       <c r="F2" s="1">
-        <v>0.46263343095779419</v>
+        <v>0.45836246013641357</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -7671,13 +7686,13 @@
         <v>283</v>
       </c>
       <c r="D3" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E3" s="1">
-        <v>0.65079365079365081</v>
+        <v>0.63076923076923075</v>
       </c>
       <c r="F3" s="1">
-        <v>0.48054841160774231</v>
+        <v>0.48635220527648926</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -7706,13 +7721,13 @@
         <v>284</v>
       </c>
       <c r="D4" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E4" s="1">
-        <v>0.52380952380952384</v>
+        <v>0.55384615384615388</v>
       </c>
       <c r="F4" s="1">
-        <v>0.5034443736076355</v>
+        <v>0.5009605884552002</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -7741,13 +7756,13 @@
         <v>285</v>
       </c>
       <c r="D5" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E5" s="1">
-        <v>0.38095238095238088</v>
+        <v>0.38461538461538458</v>
       </c>
       <c r="F5" s="1">
-        <v>0.48952153325080872</v>
+        <v>0.49029034376144409</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -7776,13 +7791,13 @@
         <v>286</v>
       </c>
       <c r="D6" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1">
-        <v>0.20634920634920631</v>
+        <v>0.2153846153846154</v>
       </c>
       <c r="F6" s="1">
-        <v>0.40793460607528687</v>
+        <v>0.41428807377815247</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -7811,13 +7826,13 @@
         <v>287</v>
       </c>
       <c r="D7" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E7" s="1">
-        <v>0.20634920634920631</v>
+        <v>0.2153846153846154</v>
       </c>
       <c r="F7" s="1">
-        <v>0.40793460607528687</v>
+        <v>0.41428807377815247</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -7846,13 +7861,13 @@
         <v>288</v>
       </c>
       <c r="D8" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E8" s="1">
-        <v>0.031746031746031703</v>
+        <v>0.030769230769230799</v>
       </c>
       <c r="F8" s="1">
-        <v>0.17673143744468689</v>
+        <v>0.17403580248355866</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -7881,13 +7896,13 @@
         <v>289</v>
       </c>
       <c r="D9" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1">
-        <v>0.031746031746031703</v>
+        <v>0.030769230769230799</v>
       </c>
       <c r="F9" s="1">
-        <v>0.17673143744468689</v>
+        <v>0.17403580248355866</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -7916,13 +7931,13 @@
         <v>290</v>
       </c>
       <c r="D10" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E10" s="1">
-        <v>0.047619047619047603</v>
+        <v>0.046153846153846198</v>
       </c>
       <c r="F10" s="1">
-        <v>0.21466939151287079</v>
+        <v>0.21145102381706238</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -7951,7 +7966,7 @@
         <v>291</v>
       </c>
       <c r="D11" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -8030,13 +8045,13 @@
         <v>303</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.91318680362387017</v>
+        <v>0.9129032165773453</v>
       </c>
       <c r="F2" s="1">
-        <v>0.060426283627748489</v>
+        <v>0.060399685055017471</v>
       </c>
       <c r="G2" s="1">
         <v>0.69999998807907105</v>
@@ -8065,13 +8080,13 @@
         <v>304</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.86080585354632078</v>
+        <v>0.86021504623274647</v>
       </c>
       <c r="F3" s="1">
-        <v>0.10455130040645599</v>
+        <v>0.10348623245954514</v>
       </c>
       <c r="G3" s="1">
         <v>0.2222222238779068</v>
@@ -8100,13 +8115,13 @@
         <v>305</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.60439560439560436</v>
+        <v>0.60215053763440862</v>
       </c>
       <c r="F4" s="1">
-        <v>0.49168917536735535</v>
+        <v>0.49210694432258606</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -8135,13 +8150,13 @@
         <v>306</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.75641026863685024</v>
+        <v>0.75537635562240435</v>
       </c>
       <c r="F5" s="1">
-        <v>0.13277125358581543</v>
+        <v>0.13107603788375854</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -8170,13 +8185,13 @@
         <v>307</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.73534798916879596</v>
+        <v>0.73476702904188507</v>
       </c>
       <c r="F6" s="1">
-        <v>0.12209172546863556</v>
+        <v>0.12097769975662231</v>
       </c>
       <c r="G6" s="1">
         <v>0.41666665673255921</v>
@@ -8205,13 +8220,13 @@
         <v>308</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.23076923076923081</v>
+        <v>0.23655913978494619</v>
       </c>
       <c r="F7" s="1">
-        <v>0.42365926504135132</v>
+        <v>0.42727267742156983</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -8240,13 +8255,13 @@
         <v>309</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.85567766427993775</v>
+        <v>0.85591398708281974</v>
       </c>
       <c r="F8" s="1">
-        <v>0.071155354380607605</v>
+        <v>0.071078859269618988</v>
       </c>
       <c r="G8" s="1">
         <v>0.73333334922790527</v>
@@ -8275,13 +8290,13 @@
         <v>310</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.6071428571428571</v>
+        <v>0.60752688172043012</v>
       </c>
       <c r="F9" s="1">
-        <v>0.22405003011226654</v>
+        <v>0.22238165140151978</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -8310,13 +8325,13 @@
         <v>311</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.69871795144709914</v>
+        <v>0.69713261915791425</v>
       </c>
       <c r="F10" s="1">
-        <v>0.24493928253650665</v>
+        <v>0.24811637401580811</v>
       </c>
       <c r="G10" s="1">
         <v>0.25</v>
@@ -8345,13 +8360,13 @@
         <v>312</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>0.54990843003922763</v>
+        <v>0.54973118808320776</v>
       </c>
       <c r="F11" s="1">
-        <v>0.36092841625213623</v>
+        <v>0.36313086748123169</v>
       </c>
       <c r="G11" s="1">
         <v>0.090277776122093201</v>
@@ -8380,19 +8395,19 @@
         <v>155</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.70691392185923818</v>
+        <v>0.70687724249337314</v>
       </c>
       <c r="F12" s="1">
-        <v>0.1329653412103653</v>
+        <v>0.13565343618392944</v>
       </c>
       <c r="G12" s="1">
         <v>0.50555557012557983</v>
       </c>
       <c r="H12" s="1">
-        <v>0.58333331346511841</v>
+        <v>0.58194446563720703</v>
       </c>
       <c r="I12" s="1">
         <v>0.69375002384185791</v>
@@ -8459,13 +8474,13 @@
         <v>326</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.96703296703296704</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="F2" s="1">
-        <v>0.17953950166702271</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -8494,13 +8509,13 @@
         <v>327</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.98901098901098905</v>
+        <v>0.978494623655914</v>
       </c>
       <c r="F3" s="1">
-        <v>0.10482848435640335</v>
+        <v>0.14584794640541077</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -8529,13 +8544,13 @@
         <v>328</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.79120879120879117</v>
+        <v>0.77419354838709675</v>
       </c>
       <c r="F4" s="1">
-        <v>0.40869668126106262</v>
+        <v>0.42037850618362427</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -8564,13 +8579,13 @@
         <v>329</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.95604395604395609</v>
+        <v>0.956989247311828</v>
       </c>
       <c r="F5" s="1">
-        <v>0.20613306760787964</v>
+        <v>0.203980952501297</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -8599,13 +8614,13 @@
         <v>330</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.94505494505494503</v>
+        <v>0.94623655913978499</v>
       </c>
       <c r="F6" s="1">
-        <v>0.22913543879985809</v>
+        <v>0.22677280008792877</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -8634,13 +8649,13 @@
         <v>331</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.80219780219780224</v>
+        <v>0.80645161290322576</v>
       </c>
       <c r="F7" s="1">
-        <v>0.40054908394813538</v>
+        <v>0.39722034335136414</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -8669,13 +8684,13 @@
         <v>332</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.50549450549450547</v>
+        <v>0.5053763440860215</v>
       </c>
       <c r="F8" s="1">
-        <v>0.50273972749710083</v>
+        <v>0.5026809573173523</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -8704,13 +8719,13 @@
         <v>333</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F9" s="1">
-        <v>0.50128042697906494</v>
+        <v>0.50128400325775147</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -8739,13 +8754,13 @@
         <v>334</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.30769230769230771</v>
+        <v>0.31182795698924731</v>
       </c>
       <c r="F10" s="1">
-        <v>0.46409547328948975</v>
+        <v>0.46575078368186951</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -8774,13 +8789,13 @@
         <v>335</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F11" s="1">
-        <v>0.50128042697906494</v>
+        <v>0.50128400325775147</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -8809,13 +8824,13 @@
         <v>336</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.52747252747252749</v>
+        <v>0.5268817204301075</v>
       </c>
       <c r="F12" s="1">
-        <v>0.50201058387756348</v>
+        <v>0.50198298692703247</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -8844,13 +8859,13 @@
         <v>337</v>
       </c>
       <c r="D13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F13" s="1">
-        <v>0.50249683856964111</v>
+        <v>0.5024484395980835</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -8923,13 +8938,13 @@
         <v>352</v>
       </c>
       <c r="D2" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" s="1">
-        <v>0.75862068965517238</v>
+        <v>0.7668539325842697</v>
       </c>
       <c r="F2" s="1">
-        <v>0.29641333222389221</v>
+        <v>0.29144465923309326</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -8958,13 +8973,13 @@
         <v>353</v>
       </c>
       <c r="D3" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3" s="1">
-        <v>0.79261363636363635</v>
+        <v>0.78888888888888886</v>
       </c>
       <c r="F3" s="1">
-        <v>0.26862141489982605</v>
+        <v>0.2674030065536499</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -8993,13 +9008,13 @@
         <v>354</v>
       </c>
       <c r="D4" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" s="1">
-        <v>0.75287356321839083</v>
+        <v>0.7528089887640449</v>
       </c>
       <c r="F4" s="1">
-        <v>0.2865549623966217</v>
+        <v>0.28577640652656555</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -9028,13 +9043,13 @@
         <v>355</v>
       </c>
       <c r="D5" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E5" s="1">
-        <v>0.66954022988505746</v>
+        <v>0.6741573033707865</v>
       </c>
       <c r="F5" s="1">
-        <v>0.30617257952690125</v>
+        <v>0.30246266722679138</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -9063,13 +9078,13 @@
         <v>356</v>
       </c>
       <c r="D6" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E6" s="1">
-        <v>0.62215909090909094</v>
+        <v>0.60833333333333328</v>
       </c>
       <c r="F6" s="1">
-        <v>0.30084726214408875</v>
+        <v>0.30226206779479981</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -9098,13 +9113,13 @@
         <v>357</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.6071428571428571</v>
+        <v>0.61021505376344087</v>
       </c>
       <c r="F7" s="1">
-        <v>0.20118695497512817</v>
+        <v>0.20007595419883728</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -9133,13 +9148,13 @@
         <v>358</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.61813186813186816</v>
+        <v>0.62096774193548388</v>
       </c>
       <c r="F8" s="1">
-        <v>0.20527982711791992</v>
+        <v>0.20394513010978699</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -9168,13 +9183,13 @@
         <v>359</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>2.494505494505495</v>
+        <v>2.4946236559139781</v>
       </c>
       <c r="F9" s="1">
-        <v>1.0260347127914429</v>
+        <v>1.0174953937530518</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -9203,13 +9218,13 @@
         <v>360</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.49890109890109891</v>
+        <v>0.49892473118279568</v>
       </c>
       <c r="F10" s="1">
-        <v>0.20520694553852081</v>
+        <v>0.20349907875061035</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -9238,13 +9253,13 @@
         <v>361</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>1.703296703296703</v>
+        <v>1.698924731182796</v>
       </c>
       <c r="F11" s="1">
-        <v>1.1689929962158203</v>
+        <v>1.1775522232055664</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -9273,13 +9288,13 @@
         <v>362</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.74725274725274726</v>
+        <v>0.74193548387096775</v>
       </c>
       <c r="F12" s="1">
-        <v>0.43699496984481812</v>
+        <v>0.43994134664535522</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -9308,13 +9323,13 @@
         <v>363</v>
       </c>
       <c r="D13" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E13" s="1">
-        <v>0.67441860465116277</v>
+        <v>0.67329545454545459</v>
       </c>
       <c r="F13" s="1">
-        <v>0.29721692204475403</v>
+        <v>0.29932382702827454</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -9343,13 +9358,13 @@
         <v>364</v>
       </c>
       <c r="D14" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E14" s="1">
-        <v>0.58522727272727271</v>
+        <v>0.58888888888888891</v>
       </c>
       <c r="F14" s="1">
-        <v>0.31687763333320618</v>
+        <v>0.31647440791130066</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -9378,25 +9393,25 @@
         <v>156</v>
       </c>
       <c r="D15" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1">
-        <v>0.65477272647095253</v>
+        <v>0.65486559055505256</v>
       </c>
       <c r="F15" s="1">
-        <v>0.18985609710216522</v>
+        <v>0.18801403045654297</v>
       </c>
       <c r="G15" s="1">
         <v>0.11999999731779099</v>
       </c>
       <c r="H15" s="1">
-        <v>0.53636366128921509</v>
+        <v>0.55909091234207153</v>
       </c>
       <c r="I15" s="1">
         <v>0.68999999761581421</v>
       </c>
       <c r="J15" s="1">
-        <v>0.81818181276321411</v>
+        <v>0.80909091234207153</v>
       </c>
       <c r="K15" s="1">
         <v>0.91818183660507202</v>
@@ -9457,13 +9472,13 @@
         <v>375</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.62637362637362637</v>
+        <v>0.62365591397849462</v>
       </c>
       <c r="F2" s="1">
-        <v>0.4864463210105896</v>
+        <v>0.48709383606910706</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -9492,13 +9507,13 @@
         <v>376</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.4175824175824176</v>
+        <v>0.40860215053763438</v>
       </c>
       <c r="F3" s="1">
-        <v>0.49589276313781738</v>
+        <v>0.49423983693122864</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -9527,13 +9542,13 @@
         <v>377</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.31868131868131872</v>
+        <v>0.32258064516129031</v>
       </c>
       <c r="F4" s="1">
-        <v>0.46854671835899353</v>
+        <v>0.46999746561050415</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -9562,13 +9577,13 @@
         <v>378</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.12087912087912089</v>
+        <v>0.1182795698924731</v>
       </c>
       <c r="F5" s="1">
-        <v>0.32779279351234436</v>
+        <v>0.32468923926353455</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -9597,13 +9612,13 @@
         <v>379</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0769230769230769</v>
+        <v>0.086021505376344107</v>
       </c>
       <c r="F6" s="1">
-        <v>0.26794564723968506</v>
+        <v>0.2819155752658844</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -9632,13 +9647,13 @@
         <v>380</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.054945054945054903</v>
+        <v>0.053763440860215103</v>
       </c>
       <c r="F7" s="1">
-        <v>0.22913543879985809</v>
+        <v>0.22677280008792877</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -9667,13 +9682,13 @@
         <v>381</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.065934065934065894</v>
+        <v>0.064516129032258104</v>
       </c>
       <c r="F8" s="1">
-        <v>0.24954169988632202</v>
+        <v>0.24700164794921875</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -9702,13 +9717,13 @@
         <v>382</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.010989010989011</v>
+        <v>0.010752688172042999</v>
       </c>
       <c r="F9" s="1">
-        <v>0.10482848435640335</v>
+        <v>0.10369516909122467</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -9737,13 +9752,13 @@
         <v>383</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.010989010989011</v>
+        <v>0.010752688172042999</v>
       </c>
       <c r="F10" s="1">
-        <v>0.10482848435640335</v>
+        <v>0.10369516909122467</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -9816,13 +9831,13 @@
         <v>393</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.76923076923076927</v>
+        <v>0.76344086021505375</v>
       </c>
       <c r="F2" s="1">
-        <v>0.42365926504135132</v>
+        <v>0.42727267742156983</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -9851,13 +9866,13 @@
         <v>394</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.69230769230769229</v>
+        <v>0.69892473118279575</v>
       </c>
       <c r="F3" s="1">
-        <v>0.46409547328948975</v>
+        <v>0.4612116813659668</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -9886,13 +9901,13 @@
         <v>395</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.48351648351648352</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="F4" s="1">
-        <v>0.50249683856964111</v>
+        <v>0.5024484395980835</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -9921,13 +9936,13 @@
         <v>396</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.14285714285714279</v>
+        <v>0.15053763440860221</v>
       </c>
       <c r="F5" s="1">
-        <v>0.35186576843261719</v>
+        <v>0.35953584313392639</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -9956,13 +9971,13 @@
         <v>397</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.17582417582417581</v>
+        <v>0.17204301075268821</v>
       </c>
       <c r="F6" s="1">
-        <v>0.38277950882911682</v>
+        <v>0.37946346402168274</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -9991,13 +10006,13 @@
         <v>398</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.054945054945054903</v>
+        <v>0.053763440860215103</v>
       </c>
       <c r="F7" s="1">
-        <v>0.22913543879985809</v>
+        <v>0.22677280008792877</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -10026,13 +10041,13 @@
         <v>399</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.1318681318681319</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="F8" s="1">
-        <v>0.34022185206413269</v>
+        <v>0.33705264329910278</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -10061,13 +10076,13 @@
         <v>400</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.043010752688171998</v>
       </c>
       <c r="F9" s="1">
-        <v>0.20613306760787964</v>
+        <v>0.203980952501297</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -10110,10 +10125,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1">
-        <v>43.956043243408203</v>
+        <v>44.086021423339844</v>
       </c>
     </row>
     <row r="3">
@@ -10124,7 +10139,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="1">
-        <v>30.769229888916016</v>
+        <v>30.107526779174805</v>
       </c>
     </row>
     <row r="4">
@@ -10132,10 +10147,10 @@
         <v>34</v>
       </c>
       <c r="B4" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
-        <v>25.274724960327149</v>
+        <v>25.806451797485352</v>
       </c>
     </row>
   </sheetData>
@@ -10193,13 +10208,13 @@
         <v>414</v>
       </c>
       <c r="D2" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2" s="1">
-        <v>0.76162790697674421</v>
+        <v>0.74715909090909094</v>
       </c>
       <c r="F2" s="1">
-        <v>0.281558096408844</v>
+        <v>0.29481709003448486</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -10208,7 +10223,7 @@
         <v>0.5</v>
       </c>
       <c r="I2" s="1">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
@@ -10228,13 +10243,13 @@
         <v>415</v>
       </c>
       <c r="D3" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3" s="1">
-        <v>0.45170454545454553</v>
+        <v>0.46111111111111108</v>
       </c>
       <c r="F3" s="1">
-        <v>0.2676471471786499</v>
+        <v>0.27001640200614929</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -10263,13 +10278,13 @@
         <v>416</v>
       </c>
       <c r="D4" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4" s="1">
-        <v>0.42897727272727271</v>
+        <v>0.42222222222222222</v>
       </c>
       <c r="F4" s="1">
-        <v>0.28097957372665405</v>
+        <v>0.27703395485877991</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -10281,7 +10296,7 @@
         <v>0.25</v>
       </c>
       <c r="J4" s="1">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
@@ -10298,13 +10313,13 @@
         <v>417</v>
       </c>
       <c r="D5" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E5" s="1">
-        <v>0.7443820224719101</v>
+        <v>0.74725274725274726</v>
       </c>
       <c r="F5" s="1">
-        <v>0.28198143839836121</v>
+        <v>0.28011530637741089</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -10333,13 +10348,13 @@
         <v>418</v>
       </c>
       <c r="D6" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E6" s="1">
-        <v>0.69827586206896552</v>
+        <v>0.702247191011236</v>
       </c>
       <c r="F6" s="1">
-        <v>0.30293604731559753</v>
+        <v>0.30122005939483643</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -10368,13 +10383,13 @@
         <v>419</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.59408602150537637</v>
       </c>
       <c r="F7" s="1">
-        <v>0.21294349431991577</v>
+        <v>0.21147122979164124</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -10403,13 +10418,13 @@
         <v>420</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.58241758241758246</v>
+        <v>0.58602150537634412</v>
       </c>
       <c r="F8" s="1">
-        <v>0.2268594354391098</v>
+        <v>0.2257072925567627</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -10438,13 +10453,13 @@
         <v>421</v>
       </c>
       <c r="D9" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1">
-        <v>0.71698113207547165</v>
+        <v>0.71818181818181814</v>
       </c>
       <c r="F9" s="1">
-        <v>0.41031688451766968</v>
+        <v>0.4055590033531189</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -10473,13 +10488,13 @@
         <v>422</v>
       </c>
       <c r="D10" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1">
-        <v>0.69090909090909092</v>
+        <v>0.6875</v>
       </c>
       <c r="F10" s="1">
-        <v>0.4248192310333252</v>
+        <v>0.42171189188957214</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -10508,13 +10523,13 @@
         <v>423</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>2.3406593406593408</v>
+        <v>2.354838709677419</v>
       </c>
       <c r="F11" s="1">
-        <v>1.2491755485534668</v>
+        <v>1.2652990818023682</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -10543,13 +10558,13 @@
         <v>424</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>1.571428571428571</v>
+        <v>1.559139784946237</v>
       </c>
       <c r="F12" s="1">
-        <v>1.1560744047164917</v>
+        <v>1.1559145450592041</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -10578,13 +10593,13 @@
         <v>425</v>
       </c>
       <c r="D13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.30107526881720431</v>
       </c>
       <c r="F13" s="1">
-        <v>0.45933538675308228</v>
+        <v>0.4612116813659668</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -10613,13 +10628,13 @@
         <v>157</v>
       </c>
       <c r="D14" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.615209507205153</v>
       </c>
       <c r="F14" s="1">
-        <v>0.15389686822891235</v>
+        <v>0.15164907276630402</v>
       </c>
       <c r="G14" s="1">
         <v>0.2222222238779068</v>
@@ -10631,7 +10646,7 @@
         <v>0.6111111044883728</v>
       </c>
       <c r="J14" s="1">
-        <v>0.75</v>
+        <v>0.72222220897674561</v>
       </c>
       <c r="K14" s="1">
         <v>0.8928571343421936</v>
@@ -10692,13 +10707,13 @@
         <v>435</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.8351648351648352</v>
+        <v>0.83870967741935487</v>
       </c>
       <c r="F2" s="1">
-        <v>0.3730873167514801</v>
+        <v>0.36979201436042786</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -10727,13 +10742,13 @@
         <v>436</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.69230769230769229</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F3" s="1">
-        <v>0.46409547328948975</v>
+        <v>0.46575078368186951</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -10762,13 +10777,13 @@
         <v>437</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.48351648351648352</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="F4" s="1">
-        <v>0.50249683856964111</v>
+        <v>0.5024484395980835</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -10797,13 +10812,13 @@
         <v>438</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.2087912087912088</v>
+        <v>0.21505376344086019</v>
       </c>
       <c r="F5" s="1">
-        <v>0.40869668126106262</v>
+        <v>0.41308653354644775</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -10832,13 +10847,13 @@
         <v>439</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0769230769230769</v>
+        <v>0.086021505376344107</v>
       </c>
       <c r="F6" s="1">
-        <v>0.26794564723968506</v>
+        <v>0.2819155752658844</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -10867,13 +10882,13 @@
         <v>440</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.043010752688171998</v>
       </c>
       <c r="F7" s="1">
-        <v>0.20613306760787964</v>
+        <v>0.203980952501297</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -10902,7 +10917,7 @@
         <v>441</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -10937,7 +10952,7 @@
         <v>442</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -11016,13 +11031,13 @@
         <v>455</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F2" s="1">
-        <v>0.50249683856964111</v>
+        <v>0.5024484395980835</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -11051,13 +11066,13 @@
         <v>456</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.45054945054945062</v>
+        <v>0.43010752688172038</v>
       </c>
       <c r="F3" s="1">
-        <v>0.50030517578125</v>
+        <v>0.4977743923664093</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -11086,13 +11101,13 @@
         <v>457</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.23076923076923081</v>
+        <v>0.24731182795698919</v>
       </c>
       <c r="F4" s="1">
-        <v>0.42365926504135132</v>
+        <v>0.433788001537323</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -11121,13 +11136,13 @@
         <v>458</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.18681318681318679</v>
+        <v>0.18279569892473119</v>
       </c>
       <c r="F5" s="1">
-        <v>0.39192086458206177</v>
+        <v>0.38859379291534424</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -11156,13 +11171,13 @@
         <v>459</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.054945054945054903</v>
+        <v>0.053763440860215103</v>
       </c>
       <c r="F6" s="1">
-        <v>0.22913543879985809</v>
+        <v>0.22677280008792877</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -11191,13 +11206,13 @@
         <v>460</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.010989010989011</v>
+        <v>0.010752688172042999</v>
       </c>
       <c r="F7" s="1">
-        <v>0.10482848435640335</v>
+        <v>0.10369516909122467</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -11226,13 +11241,13 @@
         <v>461</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.032967032967033003</v>
+        <v>0.032258064516128997</v>
       </c>
       <c r="F8" s="1">
-        <v>0.17953950166702271</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -11261,13 +11276,13 @@
         <v>462</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.043010752688171998</v>
       </c>
       <c r="F9" s="1">
-        <v>0.20613306760787964</v>
+        <v>0.203980952501297</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -11296,13 +11311,13 @@
         <v>463</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.010989010989011</v>
+        <v>0.010752688172042999</v>
       </c>
       <c r="F10" s="1">
-        <v>0.10482848435640335</v>
+        <v>0.10369516909122467</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -11331,13 +11346,13 @@
         <v>464</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>0.032967032967033003</v>
+        <v>0.032258064516128997</v>
       </c>
       <c r="F11" s="1">
-        <v>0.17953950166702271</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -11366,13 +11381,13 @@
         <v>465</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.30107526881720431</v>
       </c>
       <c r="F12" s="1">
-        <v>0.45933538675308228</v>
+        <v>0.4612116813659668</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -11445,13 +11460,13 @@
         <v>482</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.68681318681318682</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F2" s="1">
-        <v>0.37004768848419189</v>
+        <v>0.36797019839286804</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -11480,13 +11495,13 @@
         <v>483</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.30219780219780218</v>
+        <v>0.30286738351254477</v>
       </c>
       <c r="F3" s="1">
-        <v>0.19069737195968628</v>
+        <v>0.19026145339012146</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -11515,13 +11530,13 @@
         <v>484</v>
       </c>
       <c r="D4" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E4" s="1">
-        <v>0.71710526315789469</v>
+        <v>0.71153846153846157</v>
       </c>
       <c r="F4" s="1">
-        <v>0.34962385892868042</v>
+        <v>0.34677764773368836</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -11550,13 +11565,13 @@
         <v>485</v>
       </c>
       <c r="D5" s="1">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E5" s="1">
-        <v>0.6785714285714286</v>
+        <v>0.67721518987341767</v>
       </c>
       <c r="F5" s="1">
-        <v>0.2654971182346344</v>
+        <v>0.26297089457511902</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -11585,13 +11600,13 @@
         <v>486</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.3177655677655678</v>
+        <v>0.31989247311827962</v>
       </c>
       <c r="F6" s="1">
-        <v>0.23924781382083893</v>
+        <v>0.24211300909519196</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -11620,13 +11635,13 @@
         <v>487</v>
       </c>
       <c r="D7" s="1">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1">
-        <v>0.59740259740259738</v>
+        <v>0.59493670886075944</v>
       </c>
       <c r="F7" s="1">
-        <v>0.29568120837211609</v>
+        <v>0.29770433902740479</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -11655,13 +11670,13 @@
         <v>488</v>
       </c>
       <c r="D8" s="1">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1">
-        <v>0.66558441558441561</v>
+        <v>0.66455696202531645</v>
       </c>
       <c r="F8" s="1">
-        <v>0.3051379919052124</v>
+        <v>0.30193307995796204</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -11690,13 +11705,13 @@
         <v>489</v>
       </c>
       <c r="D9" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E9" s="1">
-        <v>0.67763157894736847</v>
+        <v>0.67307692307692313</v>
       </c>
       <c r="F9" s="1">
-        <v>0.32356294989585876</v>
+        <v>0.32058107852935791</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -11725,13 +11740,13 @@
         <v>490</v>
       </c>
       <c r="D10" s="1">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E10" s="1">
-        <v>0.012987012987013</v>
+        <v>0.0126582278481013</v>
       </c>
       <c r="F10" s="1">
-        <v>0.11396057903766632</v>
+        <v>0.11250878870487213</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -11760,13 +11775,13 @@
         <v>491</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>2.285714285714286</v>
+        <v>2.301075268817204</v>
       </c>
       <c r="F11" s="1">
-        <v>0.92238473892211914</v>
+        <v>0.91823256015777588</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -11795,13 +11810,13 @@
         <v>492</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.065934065934065894</v>
+        <v>0.064516129032258104</v>
       </c>
       <c r="F12" s="1">
-        <v>0.24954169988632202</v>
+        <v>0.24700164794921875</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -11830,13 +11845,13 @@
         <v>493</v>
       </c>
       <c r="D13" s="1">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1">
-        <v>0.69333333333333336</v>
+        <v>0.69480519480519476</v>
       </c>
       <c r="F13" s="1">
-        <v>0.35729211568832397</v>
+        <v>0.35500040650367737</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -11865,13 +11880,13 @@
         <v>494</v>
       </c>
       <c r="D14" s="1">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E14" s="1">
-        <v>0.59333333333333338</v>
+        <v>0.59740259740259738</v>
       </c>
       <c r="F14" s="1">
-        <v>0.41665765643119812</v>
+        <v>0.41389486193656921</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -11900,13 +11915,13 @@
         <v>495</v>
       </c>
       <c r="D15" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1">
-        <v>0.58333333333333337</v>
+        <v>0.5892857142857143</v>
       </c>
       <c r="F15" s="1">
-        <v>0.37302941083908081</v>
+        <v>0.37059095501899719</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -11935,13 +11950,13 @@
         <v>496</v>
       </c>
       <c r="D16" s="1">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E16" s="1">
-        <v>0.55223880597014929</v>
+        <v>0.55434782608695654</v>
       </c>
       <c r="F16" s="1">
-        <v>0.26663345098495483</v>
+        <v>0.26384308934211731</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -11970,25 +11985,25 @@
         <v>158</v>
       </c>
       <c r="D17" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E17" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.52456441365422746</v>
       </c>
       <c r="F17" s="1">
-        <v>0.23968173563480377</v>
+        <v>0.23781652748584747</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0.4444444477558136</v>
+        <v>0.44696968793869019</v>
       </c>
       <c r="I17" s="1">
         <v>0.60416668653488159</v>
       </c>
       <c r="J17" s="1">
-        <v>0.6736111044883728</v>
+        <v>0.66666668653488159</v>
       </c>
       <c r="K17" s="1">
         <v>0.8611111044883728</v>
@@ -12049,13 +12064,13 @@
         <v>507</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.75824175824175821</v>
+        <v>0.76344086021505375</v>
       </c>
       <c r="F2" s="1">
-        <v>0.43052059412002564</v>
+        <v>0.42727267742156983</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -12084,13 +12099,13 @@
         <v>508</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.78021978021978022</v>
+        <v>0.77419354838709675</v>
       </c>
       <c r="F3" s="1">
-        <v>0.41639184951782227</v>
+        <v>0.42037850618362427</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -12119,13 +12134,13 @@
         <v>509</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.55913978494623651</v>
       </c>
       <c r="F4" s="1">
-        <v>0.50128042697906494</v>
+        <v>0.49918118119239807</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -12154,13 +12169,13 @@
         <v>510</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0769230769230769</v>
+        <v>0.075268817204301106</v>
       </c>
       <c r="F5" s="1">
-        <v>0.26794564723968506</v>
+        <v>0.26525455713272095</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -12189,13 +12204,13 @@
         <v>511</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0769230769230769</v>
+        <v>0.075268817204301106</v>
       </c>
       <c r="F6" s="1">
-        <v>0.26794564723968506</v>
+        <v>0.26525455713272095</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -12224,13 +12239,13 @@
         <v>512</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.010989010989011</v>
+        <v>0.010752688172042999</v>
       </c>
       <c r="F7" s="1">
-        <v>0.10482848435640335</v>
+        <v>0.10369516909122467</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -12259,13 +12274,13 @@
         <v>513</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.032967032967033003</v>
+        <v>0.032258064516128997</v>
       </c>
       <c r="F8" s="1">
-        <v>0.17953950166702271</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -12294,13 +12309,13 @@
         <v>514</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.010989010989011</v>
+        <v>0.010752688172042999</v>
       </c>
       <c r="F9" s="1">
-        <v>0.10482848435640335</v>
+        <v>0.10369516909122467</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -12329,13 +12344,13 @@
         <v>515</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.065934065934065894</v>
+        <v>0.064516129032258104</v>
       </c>
       <c r="F10" s="1">
-        <v>0.24954169988632202</v>
+        <v>0.24700164794921875</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -12408,13 +12423,13 @@
         <v>531</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.89560439560439564</v>
+        <v>0.89784946236559138</v>
       </c>
       <c r="F2" s="1">
-        <v>0.20434834063053131</v>
+        <v>0.20268765091896057</v>
       </c>
       <c r="G2" s="1">
         <v>0.5</v>
@@ -12443,13 +12458,13 @@
         <v>532</v>
       </c>
       <c r="D3" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E3" s="1">
-        <v>0.67816091954022984</v>
+        <v>0.6882022471910112</v>
       </c>
       <c r="F3" s="1">
-        <v>0.30951023101806641</v>
+        <v>0.30683711171150208</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -12478,13 +12493,13 @@
         <v>533</v>
       </c>
       <c r="D4" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" s="1">
-        <v>0.70977011494252873</v>
+        <v>0.7106741573033708</v>
       </c>
       <c r="F4" s="1">
-        <v>0.2875153124332428</v>
+        <v>0.28677991032600403</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -12513,13 +12528,13 @@
         <v>534</v>
       </c>
       <c r="D5" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E5" s="1">
-        <v>0.77906976744186052</v>
+        <v>0.77840909090909094</v>
       </c>
       <c r="F5" s="1">
-        <v>0.26958194375038147</v>
+        <v>0.26918303966522217</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -12548,13 +12563,13 @@
         <v>535</v>
       </c>
       <c r="D6" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E6" s="1">
-        <v>0.9555555555555556</v>
+        <v>0.95652173913043481</v>
       </c>
       <c r="F6" s="1">
-        <v>0.2072349339723587</v>
+        <v>0.20504856109619141</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -12583,13 +12598,13 @@
         <v>536</v>
       </c>
       <c r="D7" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E7" s="1">
-        <v>0.73837209302325579</v>
+        <v>0.73863636363636365</v>
       </c>
       <c r="F7" s="1">
-        <v>0.29181727766990662</v>
+        <v>0.29092869162559509</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -12618,13 +12633,13 @@
         <v>537</v>
       </c>
       <c r="D8" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E8" s="1">
-        <v>0.62488372093023259</v>
+        <v>0.6219318181818182</v>
       </c>
       <c r="F8" s="1">
-        <v>0.31763368844985962</v>
+        <v>0.31555774807929993</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -12653,13 +12668,13 @@
         <v>538</v>
       </c>
       <c r="D9" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1">
-        <v>0.89302325581395348</v>
+        <v>0.88977272727272727</v>
       </c>
       <c r="F9" s="1">
-        <v>0.26381397247314453</v>
+        <v>0.26437512040138245</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -12688,13 +12703,13 @@
         <v>539</v>
       </c>
       <c r="D10" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1">
-        <v>0.58720930232558144</v>
+        <v>0.59375</v>
       </c>
       <c r="F10" s="1">
-        <v>0.22284075617790222</v>
+        <v>0.21877565979957581</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -12723,13 +12738,13 @@
         <v>540</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>0.55769230769230771</v>
+        <v>0.55645161290322576</v>
       </c>
       <c r="F11" s="1">
-        <v>0.22072142362594605</v>
+        <v>0.22155892848968506</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -12758,13 +12773,13 @@
         <v>541</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>1.4175824175824181</v>
+        <v>1.4086021505376341</v>
       </c>
       <c r="F12" s="1">
-        <v>1.0335046052932739</v>
+        <v>1.0345820188522339</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -12793,13 +12808,13 @@
         <v>542</v>
       </c>
       <c r="D13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
-        <v>0.26373626373626369</v>
+        <v>0.26881720430107531</v>
       </c>
       <c r="F13" s="1">
-        <v>0.44309931993484497</v>
+        <v>0.44574767351150513</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -12828,19 +12843,19 @@
         <v>543</v>
       </c>
       <c r="D14" s="1">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E14" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.84558823529411764</v>
       </c>
       <c r="F14" s="1">
-        <v>0.30801266431808472</v>
+        <v>0.28984495997428894</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
@@ -12863,13 +12878,13 @@
         <v>544</v>
       </c>
       <c r="D15" s="1">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E15" s="1">
-        <v>0.81060606060606055</v>
+        <v>0.82352941176470584</v>
       </c>
       <c r="F15" s="1">
-        <v>0.33701348304748535</v>
+        <v>0.32050225138664246</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -12898,25 +12913,25 @@
         <v>159</v>
       </c>
       <c r="D16" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1">
-        <v>0.74512531829404305</v>
+        <v>0.7479093616367668</v>
       </c>
       <c r="F16" s="1">
-        <v>0.13126222789287567</v>
+        <v>0.1331535279750824</v>
       </c>
       <c r="G16" s="1">
         <v>0.3125</v>
       </c>
       <c r="H16" s="1">
-        <v>0.6524999737739563</v>
+        <v>0.66666668653488159</v>
       </c>
       <c r="I16" s="1">
-        <v>0.76599997282028198</v>
+        <v>0.76800000667572021</v>
       </c>
       <c r="J16" s="1">
-        <v>0.83333331346511841</v>
+        <v>0.83799999952316284</v>
       </c>
       <c r="K16" s="1">
         <v>0.9375</v>
@@ -12977,13 +12992,13 @@
         <v>556</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.58241758241758246</v>
+        <v>0.56989247311827962</v>
       </c>
       <c r="F2" s="1">
-        <v>0.49589276313781738</v>
+        <v>0.4977743923664093</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -13012,13 +13027,13 @@
         <v>557</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.43956043956043961</v>
+        <v>0.43010752688172038</v>
       </c>
       <c r="F3" s="1">
-        <v>0.49908339977264404</v>
+        <v>0.4977743923664093</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -13047,13 +13062,13 @@
         <v>558</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.30107526881720431</v>
       </c>
       <c r="F4" s="1">
-        <v>0.45933538675308228</v>
+        <v>0.4612116813659668</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -13082,13 +13097,13 @@
         <v>559</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.021978021978022001</v>
+        <v>0.032258064516128997</v>
       </c>
       <c r="F5" s="1">
-        <v>0.14742395281791687</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -13117,7 +13132,7 @@
         <v>560</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -13152,13 +13167,13 @@
         <v>561</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.010989010989011</v>
+        <v>0.010752688172042999</v>
       </c>
       <c r="F7" s="1">
-        <v>0.10482848435640335</v>
+        <v>0.10369516909122467</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -13187,13 +13202,13 @@
         <v>562</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.010989010989011</v>
+        <v>0.010752688172042999</v>
       </c>
       <c r="F8" s="1">
-        <v>0.10482848435640335</v>
+        <v>0.10369516909122467</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -13222,13 +13237,13 @@
         <v>563</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.043010752688171998</v>
       </c>
       <c r="F9" s="1">
-        <v>0.20613306760787964</v>
+        <v>0.203980952501297</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -13257,13 +13272,13 @@
         <v>564</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.010989010989011</v>
+        <v>0.010752688172042999</v>
       </c>
       <c r="F10" s="1">
-        <v>0.10482848435640335</v>
+        <v>0.10369516909122467</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -13292,13 +13307,13 @@
         <v>565</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>0.26373626373626369</v>
+        <v>0.26881720430107531</v>
       </c>
       <c r="F11" s="1">
-        <v>0.44309931993484497</v>
+        <v>0.44574767351150513</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -13371,13 +13386,13 @@
         <v>581</v>
       </c>
       <c r="D2" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" s="1">
-        <v>0.67241379310344829</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="F2" s="1">
-        <v>0.24205498397350311</v>
+        <v>0.24307309091091156</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -13406,13 +13421,13 @@
         <v>582</v>
       </c>
       <c r="D3" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E3" s="1">
-        <v>0.66954022988505746</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="F3" s="1">
-        <v>0.22713539004325867</v>
+        <v>0.22799617052078247</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -13441,13 +13456,13 @@
         <v>583</v>
       </c>
       <c r="D4" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" s="1">
-        <v>0.47988505747126442</v>
+        <v>0.4747191011235955</v>
       </c>
       <c r="F4" s="1">
-        <v>0.28585445880889893</v>
+        <v>0.2896043062210083</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -13476,13 +13491,13 @@
         <v>584</v>
       </c>
       <c r="D5" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E5" s="1">
-        <v>0.52011494252873558</v>
+        <v>0.5252808988764045</v>
       </c>
       <c r="F5" s="1">
-        <v>0.28585445880889893</v>
+        <v>0.2896043062210083</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -13511,19 +13526,19 @@
         <v>585</v>
       </c>
       <c r="D6" s="1">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E6" s="1">
-        <v>0.39204545454545447</v>
+        <v>0.39010989010989011</v>
       </c>
       <c r="F6" s="1">
-        <v>0.30275425314903259</v>
+        <v>0.30324354767799378</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
         <v>0.5</v>
@@ -13546,13 +13561,13 @@
         <v>586</v>
       </c>
       <c r="D7" s="1">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E7" s="1">
-        <v>0.60795454545454541</v>
+        <v>0.60989010989010994</v>
       </c>
       <c r="F7" s="1">
-        <v>0.30275425314903259</v>
+        <v>0.30324354767799378</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -13564,7 +13579,7 @@
         <v>0.5</v>
       </c>
       <c r="J7" s="1">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -13581,13 +13596,13 @@
         <v>587</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.60164835164835162</v>
+        <v>0.59946236559139787</v>
       </c>
       <c r="F8" s="1">
-        <v>0.1935703307390213</v>
+        <v>0.1955336332321167</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -13616,13 +13631,13 @@
         <v>588</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.59615384615384615</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="F9" s="1">
-        <v>0.21975122392177582</v>
+        <v>0.21817006170749664</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -13651,13 +13666,13 @@
         <v>589</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.12087912087912089</v>
+        <v>0.1075268817204301</v>
       </c>
       <c r="F10" s="1">
-        <v>0.32779279351234436</v>
+        <v>0.31146100163459778</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -13686,13 +13701,13 @@
         <v>590</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>0.087912087912087905</v>
+        <v>0.086021505376344107</v>
       </c>
       <c r="F11" s="1">
-        <v>0.2847357988357544</v>
+        <v>0.2819155752658844</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -13721,13 +13736,13 @@
         <v>591</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.043010752688171998</v>
       </c>
       <c r="F12" s="1">
-        <v>0.20613306760787964</v>
+        <v>0.203980952501297</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -13756,13 +13771,13 @@
         <v>592</v>
       </c>
       <c r="D13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.043010752688171998</v>
       </c>
       <c r="F13" s="1">
-        <v>0.20613306760787964</v>
+        <v>0.203980952501297</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -13791,13 +13806,13 @@
         <v>593</v>
       </c>
       <c r="D14" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1">
-        <v>0.021978021978022001</v>
+        <v>0.021505376344085999</v>
       </c>
       <c r="F14" s="1">
-        <v>0.14742395281791687</v>
+        <v>0.14584794640541077</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -13826,13 +13841,13 @@
         <v>594</v>
       </c>
       <c r="D15" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1">
-        <v>0.24175824175824179</v>
+        <v>0.24731182795698919</v>
       </c>
       <c r="F15" s="1">
-        <v>0.43052059412002564</v>
+        <v>0.433788001537323</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -13861,13 +13876,13 @@
         <v>160</v>
       </c>
       <c r="D16" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1">
-        <v>0.60293040301773571</v>
+        <v>0.60394265286384086</v>
       </c>
       <c r="F16" s="1">
-        <v>0.14762195944786072</v>
+        <v>0.14930187165737152</v>
       </c>
       <c r="G16" s="1">
         <v>0.125</v>
@@ -13940,13 +13955,13 @@
         <v>597</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.84615384615384615</v>
+        <v>0.84946236559139787</v>
       </c>
       <c r="F2" s="1">
-        <v>0.36280012130737305</v>
+        <v>0.35953584313392639</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -13975,13 +13990,13 @@
         <v>312</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.54990843003922763</v>
+        <v>0.54973118808320776</v>
       </c>
       <c r="F3" s="1">
-        <v>0.36092841625213623</v>
+        <v>0.36313086748123169</v>
       </c>
       <c r="G3" s="1">
         <v>0.090277776122093201</v>
@@ -14010,13 +14025,13 @@
         <v>332</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.50549450549450547</v>
+        <v>0.5053763440860215</v>
       </c>
       <c r="F4" s="1">
-        <v>0.50273972749710083</v>
+        <v>0.5026809573173523</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -14045,13 +14060,13 @@
         <v>333</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F5" s="1">
-        <v>0.50128042697906494</v>
+        <v>0.50128400325775147</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -14080,13 +14095,13 @@
         <v>334</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.30769230769230771</v>
+        <v>0.31182795698924731</v>
       </c>
       <c r="F6" s="1">
-        <v>0.46409547328948975</v>
+        <v>0.46575078368186951</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -14115,13 +14130,13 @@
         <v>335</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F7" s="1">
-        <v>0.50128042697906494</v>
+        <v>0.50128400325775147</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -14150,13 +14165,13 @@
         <v>336</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.52747252747252749</v>
+        <v>0.5268817204301075</v>
       </c>
       <c r="F8" s="1">
-        <v>0.50201058387756348</v>
+        <v>0.50198298692703247</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -14185,13 +14200,13 @@
         <v>337</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F9" s="1">
-        <v>0.50249683856964111</v>
+        <v>0.5024484395980835</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -14220,13 +14235,13 @@
         <v>161</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.69959678268560799</v>
       </c>
       <c r="F10" s="1">
-        <v>0.22323413193225861</v>
+        <v>0.223537877202034</v>
       </c>
       <c r="G10" s="1">
         <v>0.1770833283662796</v>
@@ -14299,13 +14314,13 @@
         <v>616</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.61263736263736268</v>
+        <v>0.61021505376344087</v>
       </c>
       <c r="F2" s="1">
-        <v>0.22749766707420349</v>
+        <v>0.22860150039196015</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -14334,13 +14349,13 @@
         <v>617</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.64835164835164838</v>
+        <v>0.64784946236559138</v>
       </c>
       <c r="F3" s="1">
-        <v>0.18994890153408051</v>
+        <v>0.195869579911232</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -14369,13 +14384,13 @@
         <v>618</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.75549450549450547</v>
+        <v>0.7553763440860215</v>
       </c>
       <c r="F4" s="1">
-        <v>0.15355971455574036</v>
+        <v>0.15629236400127411</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -14404,13 +14419,13 @@
         <v>619</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.5357142857142857</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F5" s="1">
-        <v>0.29947042465209961</v>
+        <v>0.30159503221511841</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -14439,13 +14454,13 @@
         <v>620</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.40659340659340659</v>
+        <v>0.40860215053763438</v>
       </c>
       <c r="F6" s="1">
-        <v>0.23466391861438751</v>
+        <v>0.23540247976779938</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -14474,13 +14489,13 @@
         <v>621</v>
       </c>
       <c r="D7" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7" s="1">
-        <v>0.68611111111111112</v>
+        <v>0.68478260869565222</v>
       </c>
       <c r="F7" s="1">
-        <v>0.18191054463386536</v>
+        <v>0.18107420206069946</v>
       </c>
       <c r="G7" s="1">
         <v>0.25</v>
@@ -14509,13 +14524,13 @@
         <v>622</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.71153846153846157</v>
+        <v>0.70967741935483875</v>
       </c>
       <c r="F8" s="1">
-        <v>0.20042689144611359</v>
+        <v>0.19949093461036682</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -14544,13 +14559,13 @@
         <v>623</v>
       </c>
       <c r="D9" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E9" s="1">
-        <v>0.70277777777777772</v>
+        <v>0.70652173913043481</v>
       </c>
       <c r="F9" s="1">
-        <v>0.19070553779602051</v>
+        <v>0.19118160009384155</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -14579,13 +14594,13 @@
         <v>624</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.30769230769230771</v>
+        <v>0.30645161290322581</v>
       </c>
       <c r="F10" s="1">
-        <v>0.30294141173362732</v>
+        <v>0.30200648307800293</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -14614,13 +14629,13 @@
         <v>625</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>2.098901098901099</v>
+        <v>2.096774193548387</v>
       </c>
       <c r="F11" s="1">
-        <v>0.86992907524108887</v>
+        <v>0.86054223775863647</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -14649,13 +14664,13 @@
         <v>626</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.26236263736263738</v>
+        <v>0.26209677419354838</v>
       </c>
       <c r="F12" s="1">
-        <v>0.10874113440513611</v>
+        <v>0.10756777971982956</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -14684,13 +14699,13 @@
         <v>627</v>
       </c>
       <c r="D13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
-        <v>0.021978021978022001</v>
+        <v>0.021505376344085999</v>
       </c>
       <c r="F13" s="1">
-        <v>0.14742395281791687</v>
+        <v>0.14584794640541077</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -14719,13 +14734,13 @@
         <v>628</v>
       </c>
       <c r="D14" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1">
-        <v>1.395604395604396</v>
+        <v>1.387096774193548</v>
       </c>
       <c r="F14" s="1">
-        <v>1.0633189678192139</v>
+        <v>1.0635488033294678</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -14754,13 +14769,13 @@
         <v>629</v>
       </c>
       <c r="D15" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.30107526881720431</v>
       </c>
       <c r="F15" s="1">
-        <v>0.45933538675308228</v>
+        <v>0.4612116813659668</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -14789,13 +14804,13 @@
         <v>630</v>
       </c>
       <c r="D16" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1">
-        <v>0.45054945054945062</v>
+        <v>0.45161290322580638</v>
       </c>
       <c r="F16" s="1">
-        <v>0.50030517578125</v>
+        <v>0.50035053491592407</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -14824,13 +14839,13 @@
         <v>631</v>
       </c>
       <c r="D17" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E17" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="F17" s="1">
-        <v>0.2286687046289444</v>
+        <v>0.22731973230838776</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -14859,13 +14874,13 @@
         <v>632</v>
       </c>
       <c r="D18" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E18" s="1">
-        <v>0.58791208791208793</v>
+        <v>0.59139784946236562</v>
       </c>
       <c r="F18" s="1">
-        <v>0.2278328686952591</v>
+        <v>0.22657944262027741</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -14894,13 +14909,13 @@
         <v>633</v>
       </c>
       <c r="D19" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" s="1">
-        <v>0.92307692307692313</v>
+        <v>0.92473118279569888</v>
       </c>
       <c r="F19" s="1">
-        <v>0.26794564723968506</v>
+        <v>0.26525455713272095</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -14929,13 +14944,13 @@
         <v>162</v>
       </c>
       <c r="D20" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E20" s="1">
-        <v>0.6187458378928048</v>
+        <v>0.61955237837247956</v>
       </c>
       <c r="F20" s="1">
-        <v>0.11306894570589066</v>
+        <v>0.11352553963661194</v>
       </c>
       <c r="G20" s="1">
         <v>0.28125</v>
@@ -14981,13 +14996,13 @@
         <v>35</v>
       </c>
       <c r="B2" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>73.626373291015625</v>
+        <v>73.118278503417969</v>
       </c>
     </row>
     <row r="3">
@@ -14995,13 +15010,13 @@
         <v>57</v>
       </c>
       <c r="B3" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D3" s="1">
-        <v>26.373626708984375</v>
+        <v>26.881719589233398</v>
       </c>
     </row>
   </sheetData>
@@ -15059,13 +15074,13 @@
         <v>644</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.8571428571428571</v>
+        <v>0.86021505376344087</v>
       </c>
       <c r="F2" s="1">
-        <v>0.35186576843261719</v>
+        <v>0.34864327311515808</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -15094,13 +15109,13 @@
         <v>645</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.30769230769230771</v>
+        <v>0.31182795698924731</v>
       </c>
       <c r="F3" s="1">
-        <v>0.46409547328948975</v>
+        <v>0.46575078368186951</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -15129,13 +15144,13 @@
         <v>646</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F4" s="1">
-        <v>0.50249683856964111</v>
+        <v>0.5024484395980835</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -15164,13 +15179,13 @@
         <v>647</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0769230769230769</v>
+        <v>0.075268817204301106</v>
       </c>
       <c r="F5" s="1">
-        <v>0.26794564723968506</v>
+        <v>0.26525455713272095</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -15199,13 +15214,13 @@
         <v>648</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.2087912087912088</v>
+        <v>0.20430107526881719</v>
       </c>
       <c r="F6" s="1">
-        <v>0.40869668126106262</v>
+        <v>0.40537530183792114</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -15234,13 +15249,13 @@
         <v>649</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.0769230769230769</v>
+        <v>0.075268817204301106</v>
       </c>
       <c r="F7" s="1">
-        <v>0.26794564723968506</v>
+        <v>0.26525455713272095</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -15269,13 +15284,13 @@
         <v>650</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.021978021978022001</v>
+        <v>0.021505376344085999</v>
       </c>
       <c r="F8" s="1">
-        <v>0.14742395281791687</v>
+        <v>0.14584794640541077</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -15304,13 +15319,13 @@
         <v>651</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.032967032967033003</v>
+        <v>0.032258064516128997</v>
       </c>
       <c r="F9" s="1">
-        <v>0.17953950166702271</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -15339,13 +15354,13 @@
         <v>652</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.021978021978022001</v>
+        <v>0.021505376344085999</v>
       </c>
       <c r="F10" s="1">
-        <v>0.14742395281791687</v>
+        <v>0.14584794640541077</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -15418,13 +15433,13 @@
         <v>663</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.5714285714285714</v>
+        <v>0.55913978494623651</v>
       </c>
       <c r="F2" s="1">
-        <v>0.4976133406162262</v>
+        <v>0.49918118119239807</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -15453,13 +15468,13 @@
         <v>664</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.36263736263736263</v>
+        <v>0.36559139784946237</v>
       </c>
       <c r="F3" s="1">
-        <v>0.48342490196228027</v>
+        <v>0.48420590162277222</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -15488,13 +15503,13 @@
         <v>665</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.14285714285714279</v>
+        <v>0.15053763440860221</v>
       </c>
       <c r="F4" s="1">
-        <v>0.35186576843261719</v>
+        <v>0.35953584313392639</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -15523,13 +15538,13 @@
         <v>666</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.18681318681318679</v>
+        <v>0.18279569892473119</v>
       </c>
       <c r="F5" s="1">
-        <v>0.39192086458206177</v>
+        <v>0.38859379291534424</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -15558,13 +15573,13 @@
         <v>667</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.032967032967033003</v>
+        <v>0.032258064516128997</v>
       </c>
       <c r="F6" s="1">
-        <v>0.17953950166702271</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -15593,13 +15608,13 @@
         <v>668</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.032967032967033003</v>
+        <v>0.032258064516128997</v>
       </c>
       <c r="F7" s="1">
-        <v>0.17953950166702271</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -15628,13 +15643,13 @@
         <v>669</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.032967032967033003</v>
+        <v>0.032258064516128997</v>
       </c>
       <c r="F8" s="1">
-        <v>0.17953950166702271</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -15663,13 +15678,13 @@
         <v>670</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.032967032967033003</v>
+        <v>0.032258064516128997</v>
       </c>
       <c r="F9" s="1">
-        <v>0.17953950166702271</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -15698,13 +15713,13 @@
         <v>671</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.30107526881720431</v>
       </c>
       <c r="F10" s="1">
-        <v>0.45933538675308228</v>
+        <v>0.4612116813659668</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -15783,43 +15798,43 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0.31080192126500206</v>
+        <v>0.30789871176225092</v>
       </c>
       <c r="D2">
-        <v>-0.10168653808473759</v>
+        <v>-0.090223856909682973</v>
       </c>
       <c r="E2">
-        <v>0.31038387807650764</v>
+        <v>0.30786638951562317</v>
       </c>
       <c r="F2">
-        <v>0.36263277831013846</v>
+        <v>0.37985766912440888</v>
       </c>
       <c r="G2">
-        <v>0.47752385668273817</v>
+        <v>0.49111480199669499</v>
       </c>
       <c r="H2">
-        <v>0.26869150336513481</v>
+        <v>0.28831512409342264</v>
       </c>
       <c r="I2">
-        <v>0.29673536651147736</v>
+        <v>0.31932376540999813</v>
       </c>
       <c r="J2">
-        <v>0.06846918147421098</v>
+        <v>0.072655677340248318</v>
       </c>
       <c r="K2">
-        <v>0.047193773458093606</v>
+        <v>0.073614294696215568</v>
       </c>
       <c r="L2">
-        <v>0.50729690114661297</v>
+        <v>0.51989498231405018</v>
       </c>
       <c r="M2">
-        <v>0.24422080582519162</v>
+        <v>0.24973690680943997</v>
       </c>
       <c r="N2">
-        <v>0.21534225576799618</v>
+        <v>0.24225905013815116</v>
       </c>
       <c r="O2">
-        <v>0.74696292374296069</v>
+        <v>0.75578075346499107</v>
       </c>
     </row>
     <row r="3">
@@ -15827,46 +15842,46 @@
         <v>140</v>
       </c>
       <c r="B3">
-        <v>0.31080192126500206</v>
+        <v>0.30789871176225092</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>-0.46211890181322879</v>
+        <v>-0.48083678482334552</v>
       </c>
       <c r="E3">
-        <v>-0.17072396038633786</v>
+        <v>-0.1755029850530567</v>
       </c>
       <c r="F3">
-        <v>0.11122277679960589</v>
+        <v>0.10954257546367567</v>
       </c>
       <c r="G3">
-        <v>0.68099159587665758</v>
+        <v>0.68020879439313975</v>
       </c>
       <c r="H3">
-        <v>-0.13824414891210335</v>
+        <v>-0.14138569783277374</v>
       </c>
       <c r="I3">
-        <v>-0.16413728253649593</v>
+        <v>-0.18651170100007974</v>
       </c>
       <c r="J3">
-        <v>-0.27105277838815678</v>
+        <v>-0.28621005581934961</v>
       </c>
       <c r="K3">
-        <v>-0.24282845059470099</v>
+        <v>-0.25441650121289378</v>
       </c>
       <c r="L3">
-        <v>0.76925244683450622</v>
+        <v>0.76406258135960381</v>
       </c>
       <c r="M3">
-        <v>-0.28771931328754791</v>
+        <v>-0.30428756398141554</v>
       </c>
       <c r="N3">
-        <v>-0.22649842384915847</v>
+        <v>-0.24527073910542802</v>
       </c>
       <c r="O3">
-        <v>0.2396055117037327</v>
+        <v>0.22185434016387495</v>
       </c>
     </row>
     <row r="4">
@@ -15874,46 +15889,46 @@
         <v>141</v>
       </c>
       <c r="B4">
-        <v>-0.10168653808473759</v>
+        <v>-0.090223856909682973</v>
       </c>
       <c r="C4">
-        <v>-0.46211890181322879</v>
+        <v>-0.48083678482334552</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>0.29898319133148998</v>
+        <v>0.3016515470476851</v>
       </c>
       <c r="F4">
-        <v>0.052996401149953437</v>
+        <v>0.052490072783603528</v>
       </c>
       <c r="G4">
-        <v>-0.2482813959109047</v>
+        <v>-0.25308075436897398</v>
       </c>
       <c r="H4">
-        <v>0.34889584524509754</v>
+        <v>0.35693873932126219</v>
       </c>
       <c r="I4">
-        <v>0.37965296534981907</v>
+        <v>0.4074247999339366</v>
       </c>
       <c r="J4">
-        <v>0.4012729133973913</v>
+        <v>0.4222645396179609</v>
       </c>
       <c r="K4">
-        <v>0.33984790892938788</v>
+        <v>0.35767518853196423</v>
       </c>
       <c r="L4">
-        <v>-0.21878190721075338</v>
+        <v>-0.22383018118919101</v>
       </c>
       <c r="M4">
-        <v>0.60261215531087464</v>
+        <v>0.615970527552825</v>
       </c>
       <c r="N4">
-        <v>0.41398746522475172</v>
+        <v>0.43855505530517808</v>
       </c>
       <c r="O4">
-        <v>0.20929939745104564</v>
+        <v>0.22446317988753492</v>
       </c>
     </row>
     <row r="5">
@@ -15921,46 +15936,46 @@
         <v>142</v>
       </c>
       <c r="B5">
-        <v>0.31038387807650764</v>
+        <v>0.30786638951562317</v>
       </c>
       <c r="C5">
-        <v>-0.17072396038633786</v>
+        <v>-0.1755029850530567</v>
       </c>
       <c r="D5">
-        <v>0.29898319133148998</v>
+        <v>0.3016515470476851</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.6211646698726111</v>
+        <v>0.62664785544911938</v>
       </c>
       <c r="G5">
-        <v>0.16627522409985371</v>
+        <v>0.16608674985678018</v>
       </c>
       <c r="H5">
-        <v>0.64124024010259828</v>
+        <v>0.63173416552157857</v>
       </c>
       <c r="I5">
-        <v>0.57954875359847613</v>
+        <v>0.57968152933899086</v>
       </c>
       <c r="J5">
-        <v>0.24685933125266046</v>
+        <v>0.2500950822926224</v>
       </c>
       <c r="K5">
-        <v>0.51727238192396585</v>
+        <v>0.51907375385867893</v>
       </c>
       <c r="L5">
-        <v>0.25007531683681633</v>
+        <v>0.24662719412737935</v>
       </c>
       <c r="M5">
-        <v>0.79725538826906262</v>
+        <v>0.79393551609047708</v>
       </c>
       <c r="N5">
-        <v>0.63121139096497936</v>
+        <v>0.62896796519691667</v>
       </c>
       <c r="O5">
-        <v>0.68260950010477262</v>
+        <v>0.67515842496320711</v>
       </c>
     </row>
     <row r="6">
@@ -15968,46 +15983,46 @@
         <v>143</v>
       </c>
       <c r="B6">
-        <v>0.36263277831013846</v>
+        <v>0.37985766912440888</v>
       </c>
       <c r="C6">
-        <v>0.11122277679960589</v>
+        <v>0.10954257546367567</v>
       </c>
       <c r="D6">
-        <v>0.052996401149953437</v>
+        <v>0.052490072783603528</v>
       </c>
       <c r="E6">
-        <v>0.6211646698726111</v>
+        <v>0.62664785544911938</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>0.30174982818046386</v>
+        <v>0.29984646909158469</v>
       </c>
       <c r="H6">
-        <v>0.4562846628199877</v>
+        <v>0.47136651727371826</v>
       </c>
       <c r="I6">
-        <v>0.41607746155885583</v>
+        <v>0.40738849799327698</v>
       </c>
       <c r="J6">
-        <v>0.029160919178810637</v>
+        <v>0.033906370029994748</v>
       </c>
       <c r="K6">
-        <v>0.42267184082057952</v>
+        <v>0.42049349106124928</v>
       </c>
       <c r="L6">
-        <v>0.38311546135377145</v>
+        <v>0.38687501976597932</v>
       </c>
       <c r="M6">
-        <v>0.59825648555865252</v>
+        <v>0.59391481048492889</v>
       </c>
       <c r="N6">
-        <v>0.47858846600685706</v>
+        <v>0.4693647355899912</v>
       </c>
       <c r="O6">
-        <v>0.63813519354976811</v>
+        <v>0.63850905652947787</v>
       </c>
     </row>
     <row r="7">
@@ -16015,46 +16030,46 @@
         <v>144</v>
       </c>
       <c r="B7">
-        <v>0.47752385668273817</v>
+        <v>0.49111480199669499</v>
       </c>
       <c r="C7">
-        <v>0.68099159587665758</v>
+        <v>0.68020879439313975</v>
       </c>
       <c r="D7">
-        <v>-0.2482813959109047</v>
+        <v>-0.25308075436897398</v>
       </c>
       <c r="E7">
-        <v>0.16627522409985371</v>
+        <v>0.16608674985678018</v>
       </c>
       <c r="F7">
-        <v>0.30174982818046386</v>
+        <v>0.29984646909158469</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>0.13510198960077016</v>
+        <v>0.15218482918287935</v>
       </c>
       <c r="I7">
-        <v>0.080844480541973809</v>
+        <v>0.073027030878901333</v>
       </c>
       <c r="J7">
-        <v>0.02715835427757653</v>
+        <v>0.022523531830086062</v>
       </c>
       <c r="K7">
-        <v>-0.017068773155352948</v>
+        <v>-0.016855949094773965</v>
       </c>
       <c r="L7">
-        <v>0.93045509620265732</v>
+        <v>0.93155269930962237</v>
       </c>
       <c r="M7">
-        <v>0.10703051149828932</v>
+        <v>0.099070268343007306</v>
       </c>
       <c r="N7">
-        <v>0.043841057833132649</v>
+        <v>0.038866296841339763</v>
       </c>
       <c r="O7">
-        <v>0.5831301126549856</v>
+        <v>0.57972288431479702</v>
       </c>
     </row>
     <row r="8">
@@ -16062,46 +16077,46 @@
         <v>145</v>
       </c>
       <c r="B8">
-        <v>0.26869150336513481</v>
+        <v>0.28831512409342264</v>
       </c>
       <c r="C8">
-        <v>-0.13824414891210335</v>
+        <v>-0.14138569783277374</v>
       </c>
       <c r="D8">
-        <v>0.34889584524509754</v>
+        <v>0.35693873932126219</v>
       </c>
       <c r="E8">
-        <v>0.64124024010259828</v>
+        <v>0.63173416552157857</v>
       </c>
       <c r="F8">
-        <v>0.4562846628199877</v>
+        <v>0.47136651727371826</v>
       </c>
       <c r="G8">
-        <v>0.13510198960077016</v>
+        <v>0.15218482918287935</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.59100682671488802</v>
+        <v>0.61807737208780367</v>
       </c>
       <c r="J8">
-        <v>0.1889452480657407</v>
+        <v>0.1983274594984501</v>
       </c>
       <c r="K8">
-        <v>0.44600782700618891</v>
+        <v>0.47389776309491854</v>
       </c>
       <c r="L8">
-        <v>0.36454184612959895</v>
+        <v>0.37729133032672962</v>
       </c>
       <c r="M8">
-        <v>0.58808743459227708</v>
+        <v>0.59149743913197206</v>
       </c>
       <c r="N8">
-        <v>0.60331312112415614</v>
+        <v>0.63157912239826408</v>
       </c>
       <c r="O8">
-        <v>0.62856787538053582</v>
+        <v>0.64817399585153301</v>
       </c>
     </row>
     <row r="9">
@@ -16109,46 +16124,46 @@
         <v>146</v>
       </c>
       <c r="B9">
-        <v>0.29673536651147736</v>
+        <v>0.31932376540999813</v>
       </c>
       <c r="C9">
-        <v>-0.16413728253649593</v>
+        <v>-0.18651170100007974</v>
       </c>
       <c r="D9">
-        <v>0.37965296534981907</v>
+        <v>0.4074247999339366</v>
       </c>
       <c r="E9">
-        <v>0.57954875359847613</v>
+        <v>0.57968152933899086</v>
       </c>
       <c r="F9">
-        <v>0.41607746155885583</v>
+        <v>0.40738849799327698</v>
       </c>
       <c r="G9">
-        <v>0.080844480541973809</v>
+        <v>0.073027030878901333</v>
       </c>
       <c r="H9">
-        <v>0.59100682671488802</v>
+        <v>0.61807737208780367</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9">
-        <v>0.27744083581758272</v>
+        <v>0.30263037191621095</v>
       </c>
       <c r="K9">
-        <v>0.52415368172193011</v>
+        <v>0.54034369078133271</v>
       </c>
       <c r="L9">
-        <v>0.18330290733142554</v>
+        <v>0.18092643688718557</v>
       </c>
       <c r="M9">
-        <v>0.60054917408048536</v>
+        <v>0.61380925914317852</v>
       </c>
       <c r="N9">
-        <v>0.90661139025433724</v>
+        <v>0.91072796188562033</v>
       </c>
       <c r="O9">
-        <v>0.67495204762914096</v>
+        <v>0.68668953886650275</v>
       </c>
     </row>
     <row r="10">
@@ -16156,46 +16171,46 @@
         <v>147</v>
       </c>
       <c r="B10">
-        <v>0.06846918147421098</v>
+        <v>0.072655677340248318</v>
       </c>
       <c r="C10">
-        <v>-0.27105277838815678</v>
+        <v>-0.28621005581934961</v>
       </c>
       <c r="D10">
-        <v>0.4012729133973913</v>
+        <v>0.4222645396179609</v>
       </c>
       <c r="E10">
-        <v>0.24685933125266046</v>
+        <v>0.2500950822926224</v>
       </c>
       <c r="F10">
-        <v>0.029160919178810637</v>
+        <v>0.033906370029994748</v>
       </c>
       <c r="G10">
-        <v>0.02715835427757653</v>
+        <v>0.022523531830086062</v>
       </c>
       <c r="H10">
-        <v>0.1889452480657407</v>
+        <v>0.1983274594984501</v>
       </c>
       <c r="I10">
-        <v>0.27744083581758272</v>
+        <v>0.30263037191621095</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10">
-        <v>0.37280669751233003</v>
+        <v>0.38681202953495114</v>
       </c>
       <c r="L10">
-        <v>-0.027448913417786228</v>
+        <v>-0.032612221253912138</v>
       </c>
       <c r="M10">
-        <v>0.68747535549695793</v>
+        <v>0.69593962475676485</v>
       </c>
       <c r="N10">
-        <v>0.36419686166485177</v>
+        <v>0.3852103615370564</v>
       </c>
       <c r="O10">
-        <v>0.36125357941770969</v>
+        <v>0.36908511525432486</v>
       </c>
     </row>
     <row r="11">
@@ -16203,46 +16218,46 @@
         <v>148</v>
       </c>
       <c r="B11">
-        <v>0.047193773458093606</v>
+        <v>0.073614294696215568</v>
       </c>
       <c r="C11">
-        <v>-0.24282845059470099</v>
+        <v>-0.25441650121289378</v>
       </c>
       <c r="D11">
-        <v>0.33984790892938788</v>
+        <v>0.35767518853196423</v>
       </c>
       <c r="E11">
-        <v>0.51727238192396585</v>
+        <v>0.51907375385867893</v>
       </c>
       <c r="F11">
-        <v>0.42267184082057952</v>
+        <v>0.42049349106124928</v>
       </c>
       <c r="G11">
-        <v>-0.017068773155352948</v>
+        <v>-0.016855949094773965</v>
       </c>
       <c r="H11">
-        <v>0.44600782700618891</v>
+        <v>0.47389776309491854</v>
       </c>
       <c r="I11">
-        <v>0.52415368172193011</v>
+        <v>0.54034369078133271</v>
       </c>
       <c r="J11">
-        <v>0.37280669751233003</v>
+        <v>0.38681202953495114</v>
       </c>
       <c r="K11">
         <v>1</v>
       </c>
       <c r="L11">
-        <v>0.043088249442024898</v>
+        <v>0.0500128353475571</v>
       </c>
       <c r="M11">
-        <v>0.61142386705044816</v>
+        <v>0.61937149880601683</v>
       </c>
       <c r="N11">
-        <v>0.83456042848695578</v>
+        <v>0.83962833344449805</v>
       </c>
       <c r="O11">
-        <v>0.50160320664603464</v>
+        <v>0.51815860923255597</v>
       </c>
     </row>
     <row r="12">
@@ -16250,46 +16265,46 @@
         <v>149</v>
       </c>
       <c r="B12">
-        <v>0.50729690114661297</v>
+        <v>0.51989498231405018</v>
       </c>
       <c r="C12">
-        <v>0.76925244683450622</v>
+        <v>0.76406258135960381</v>
       </c>
       <c r="D12">
-        <v>-0.21878190721075338</v>
+        <v>-0.22383018118919101</v>
       </c>
       <c r="E12">
-        <v>0.25007531683681633</v>
+        <v>0.24662719412737935</v>
       </c>
       <c r="F12">
-        <v>0.38311546135377145</v>
+        <v>0.38687501976597932</v>
       </c>
       <c r="G12">
-        <v>0.93045509620265732</v>
+        <v>0.93155269930962237</v>
       </c>
       <c r="H12">
-        <v>0.36454184612959895</v>
+        <v>0.37729133032672962</v>
       </c>
       <c r="I12">
-        <v>0.18330290733142554</v>
+        <v>0.18092643688718557</v>
       </c>
       <c r="J12">
-        <v>-0.027448913417786228</v>
+        <v>-0.032612221253912138</v>
       </c>
       <c r="K12">
-        <v>0.043088249442024898</v>
+        <v>0.0500128353475571</v>
       </c>
       <c r="L12">
         <v>1</v>
       </c>
       <c r="M12">
-        <v>0.14930071038133091</v>
+        <v>0.14083620223102328</v>
       </c>
       <c r="N12">
-        <v>0.13992842747557219</v>
+        <v>0.14133777007941409</v>
       </c>
       <c r="O12">
-        <v>0.6649766720834347</v>
+        <v>0.66227382747241714</v>
       </c>
     </row>
     <row r="13">
@@ -16297,46 +16312,46 @@
         <v>150</v>
       </c>
       <c r="B13">
-        <v>0.24422080582519162</v>
+        <v>0.24973690680943997</v>
       </c>
       <c r="C13">
-        <v>-0.28771931328754791</v>
+        <v>-0.30428756398141554</v>
       </c>
       <c r="D13">
-        <v>0.60261215531087464</v>
+        <v>0.615970527552825</v>
       </c>
       <c r="E13">
-        <v>0.79725538826906262</v>
+        <v>0.79393551609047708</v>
       </c>
       <c r="F13">
-        <v>0.59825648555865252</v>
+        <v>0.59391481048492889</v>
       </c>
       <c r="G13">
-        <v>0.10703051149828932</v>
+        <v>0.099070268343007306</v>
       </c>
       <c r="H13">
-        <v>0.58808743459227708</v>
+        <v>0.59149743913197206</v>
       </c>
       <c r="I13">
-        <v>0.60054917408048536</v>
+        <v>0.61380925914317852</v>
       </c>
       <c r="J13">
-        <v>0.68747535549695793</v>
+        <v>0.69593962475676485</v>
       </c>
       <c r="K13">
-        <v>0.61142386705044816</v>
+        <v>0.61937149880601683</v>
       </c>
       <c r="L13">
-        <v>0.14930071038133091</v>
+        <v>0.14083620223102328</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13">
-        <v>0.69144721971255363</v>
+        <v>0.70022699363286456</v>
       </c>
       <c r="O13">
-        <v>0.70494437122931008</v>
+        <v>0.70375521008109399</v>
       </c>
     </row>
     <row r="14">
@@ -16344,46 +16359,46 @@
         <v>151</v>
       </c>
       <c r="B14">
-        <v>0.21534225576799618</v>
+        <v>0.24225905013815116</v>
       </c>
       <c r="C14">
-        <v>-0.22649842384915847</v>
+        <v>-0.24527073910542802</v>
       </c>
       <c r="D14">
-        <v>0.41398746522475172</v>
+        <v>0.43855505530517808</v>
       </c>
       <c r="E14">
-        <v>0.63121139096497936</v>
+        <v>0.62896796519691667</v>
       </c>
       <c r="F14">
-        <v>0.47858846600685706</v>
+        <v>0.4693647355899912</v>
       </c>
       <c r="G14">
-        <v>0.043841057833132649</v>
+        <v>0.038866296841339763</v>
       </c>
       <c r="H14">
-        <v>0.60331312112415614</v>
+        <v>0.63157912239826408</v>
       </c>
       <c r="I14">
-        <v>0.90661139025433724</v>
+        <v>0.91072796188562033</v>
       </c>
       <c r="J14">
-        <v>0.36419686166485177</v>
+        <v>0.3852103615370564</v>
       </c>
       <c r="K14">
-        <v>0.83456042848695578</v>
+        <v>0.83962833344449805</v>
       </c>
       <c r="L14">
-        <v>0.13992842747557219</v>
+        <v>0.14133777007941409</v>
       </c>
       <c r="M14">
-        <v>0.69144721971255363</v>
+        <v>0.70022699363286456</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
       <c r="O14">
-        <v>0.68516404662132224</v>
+        <v>0.69759358554241335</v>
       </c>
     </row>
     <row r="15">
@@ -16391,43 +16406,43 @@
         <v>152</v>
       </c>
       <c r="B15">
-        <v>0.74696292374296069</v>
+        <v>0.75578075346499107</v>
       </c>
       <c r="C15">
-        <v>0.2396055117037327</v>
+        <v>0.22185434016387495</v>
       </c>
       <c r="D15">
-        <v>0.20929939745104564</v>
+        <v>0.22446317988753492</v>
       </c>
       <c r="E15">
-        <v>0.68260950010477262</v>
+        <v>0.67515842496320711</v>
       </c>
       <c r="F15">
-        <v>0.63813519354976811</v>
+        <v>0.63850905652947787</v>
       </c>
       <c r="G15">
-        <v>0.5831301126549856</v>
+        <v>0.57972288431479702</v>
       </c>
       <c r="H15">
-        <v>0.62856787538053582</v>
+        <v>0.64817399585153301</v>
       </c>
       <c r="I15">
-        <v>0.67495204762914096</v>
+        <v>0.68668953886650275</v>
       </c>
       <c r="J15">
-        <v>0.36125357941770969</v>
+        <v>0.36908511525432486</v>
       </c>
       <c r="K15">
-        <v>0.50160320664603464</v>
+        <v>0.51815860923255597</v>
       </c>
       <c r="L15">
-        <v>0.6649766720834347</v>
+        <v>0.66227382747241714</v>
       </c>
       <c r="M15">
-        <v>0.70494437122931008</v>
+        <v>0.70375521008109399</v>
       </c>
       <c r="N15">
-        <v>0.68516404662132224</v>
+        <v>0.69759358554241335</v>
       </c>
       <c r="O15">
         <v>1</v>
@@ -16464,66 +16479,66 @@
         <v>153</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>0.74696292374296069</v>
+        <v>0.75578075346499107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D3" s="1">
-        <v>0.68260950010477262</v>
+        <v>0.68668953886650275</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" s="1">
-        <v>0.67495204762914096</v>
+        <v>0.67515842496320711</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D5" s="1">
-        <v>0.63813519354976811</v>
+        <v>0.64817399585153301</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" s="1">
-        <v>0.62856787538053582</v>
+        <v>0.63850905652947787</v>
       </c>
     </row>
     <row r="7">
@@ -16534,10 +16549,10 @@
         <v>158</v>
       </c>
       <c r="C7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" s="1">
-        <v>0.5831301126549856</v>
+        <v>0.57972288431479702</v>
       </c>
     </row>
     <row r="8">
@@ -16548,10 +16563,10 @@
         <v>162</v>
       </c>
       <c r="C8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" s="1">
-        <v>0.50160320664603464</v>
+        <v>0.51815860923255597</v>
       </c>
     </row>
     <row r="9">
@@ -16562,38 +16577,38 @@
         <v>161</v>
       </c>
       <c r="C9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D9" s="1">
-        <v>0.36125357941770969</v>
+        <v>0.36908511525432491</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D10" s="1">
-        <v>0.2396055117037327</v>
+        <v>0.22446317988753489</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" s="1">
-        <v>0.20929939745104559</v>
+        <v>0.22185434016387501</v>
       </c>
     </row>
   </sheetData>
@@ -16602,71 +16617,199 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D2" s="1">
+        <v>93</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.68817204301075274</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C3" t="s">
+        <v>675</v>
+      </c>
+      <c r="D3" s="1">
+        <v>69</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.55434782608695654</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" t="s">
+        <v>676</v>
+      </c>
+      <c r="D4" s="1">
+        <v>93</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.52456441365422746</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>518</v>
+      </c>
+      <c r="B5" t="s">
+        <v>532</v>
+      </c>
+      <c r="C5" t="s">
+        <v>674</v>
+      </c>
+      <c r="D5" s="1">
+        <v>89</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.6882022471910112</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>520</v>
+      </c>
+      <c r="B6" t="s">
+        <v>534</v>
+      </c>
+      <c r="C6" t="s">
+        <v>674</v>
+      </c>
+      <c r="D6" s="1">
+        <v>88</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.77840909090909094</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" t="s">
+        <v>676</v>
+      </c>
+      <c r="D7" s="1">
+        <v>93</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.7479093616367668</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:B9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B3" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B4" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B6" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B7" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B9" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -16697,10 +16840,10 @@
         <v>37</v>
       </c>
       <c r="B2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -16734,7 +16877,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="1">
-        <v>8.7912092208862305</v>
+        <v>8.6021509170532227</v>
       </c>
     </row>
     <row r="3">
@@ -16742,10 +16885,10 @@
         <v>62</v>
       </c>
       <c r="B3" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1">
-        <v>34.065933227539063</v>
+        <v>34.408603668212891</v>
       </c>
     </row>
     <row r="4">
@@ -16756,7 +16899,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="1">
-        <v>10.989010810852051</v>
+        <v>10.752688407897949</v>
       </c>
     </row>
     <row r="5">
@@ -16767,7 +16910,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>1.0989011526107788</v>
+        <v>1.0752688646316528</v>
       </c>
     </row>
     <row r="6">
@@ -16778,7 +16921,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="1">
-        <v>12.087912559509277</v>
+        <v>11.827957153320313</v>
       </c>
     </row>
     <row r="7">
@@ -16786,10 +16929,10 @@
         <v>66</v>
       </c>
       <c r="B7" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1">
-        <v>17.582418441772461</v>
+        <v>18.279569625854492</v>
       </c>
     </row>
     <row r="8">
@@ -16800,7 +16943,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="1">
-        <v>12.087912559509277</v>
+        <v>11.827957153320313</v>
       </c>
     </row>
     <row r="9">
@@ -16811,7 +16954,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>3.2967033386230469</v>
+        <v>3.225806474685669</v>
       </c>
     </row>
   </sheetData>
@@ -16851,13 +16994,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B2" s="1">
-        <v>57.037545787545803</v>
+        <v>56.585125448028656</v>
       </c>
       <c r="C2" s="1">
-        <v>50.884652758754804</v>
+        <v>50.466242631130577</v>
       </c>
       <c r="D2" s="1">
         <v>32.93333333333333</v>
@@ -16866,7 +17009,7 @@
         <v>47.366666666666667</v>
       </c>
       <c r="F2" s="1">
-        <v>62.483333333333334</v>
+        <v>62.100000000000001</v>
       </c>
       <c r="G2" s="1">
         <v>17.800000000000001</v>
@@ -16909,13 +17052,13 @@
         <v>32</v>
       </c>
       <c r="B2" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1">
-        <v>70.738333333333344</v>
+        <v>69.890650406504051</v>
       </c>
       <c r="D2" s="1">
-        <v>53.116666666666667</v>
+        <v>52.883333333333333</v>
       </c>
       <c r="E2" s="1">
         <v>20.416666666666668</v>
@@ -16932,10 +17075,10 @@
         <v>28</v>
       </c>
       <c r="C3" s="1">
-        <v>50.832142857142848</v>
+        <v>51.239880952380965</v>
       </c>
       <c r="D3" s="1">
-        <v>51.31666666666667</v>
+        <v>52.708333333333336</v>
       </c>
       <c r="E3" s="1">
         <v>17.816666666666666</v>
@@ -16949,13 +17092,13 @@
         <v>34</v>
       </c>
       <c r="B4" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
-        <v>40.764492753623195</v>
+        <v>40.09097222222222</v>
       </c>
       <c r="D4" s="1">
-        <v>33.616666666666667</v>
+        <v>33.049999999999997</v>
       </c>
       <c r="E4" s="1">
         <v>17.800000000000001</v>
@@ -17019,7 +17162,7 @@
         <v>90</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -17054,13 +17197,13 @@
         <v>91</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.1098901098901099</v>
+        <v>0.1075268817204301</v>
       </c>
       <c r="F3" s="1">
-        <v>0.31448546051979065</v>
+        <v>0.31146100163459778</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -17089,13 +17232,13 @@
         <v>92</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.054945054945054903</v>
+        <v>0.053763440860215103</v>
       </c>
       <c r="F4" s="1">
-        <v>0.22913543879985809</v>
+        <v>0.22677280008792877</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -17124,13 +17267,13 @@
         <v>93</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.032967032967033003</v>
+        <v>0.032258064516128997</v>
       </c>
       <c r="F5" s="1">
-        <v>0.17953950166702271</v>
+        <v>0.1776423454284668</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -17159,7 +17302,7 @@
         <v>94</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -17194,7 +17337,7 @@
         <v>95</v>
       </c>
       <c r="D7" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -17229,13 +17372,13 @@
         <v>96</v>
       </c>
       <c r="D8" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E8" s="1">
-        <v>0.056179775280898903</v>
+        <v>0.054945054945054903</v>
       </c>
       <c r="F8" s="1">
-        <v>0.23157320916652679</v>
+        <v>0.22913543879985809</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -17264,7 +17407,7 @@
         <v>97</v>
       </c>
       <c r="D9" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -17299,13 +17442,13 @@
         <v>98</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.2087912087912088</v>
+        <v>0.20430107526881719</v>
       </c>
       <c r="F10" s="1">
-        <v>0.40869668126106262</v>
+        <v>0.40537530183792114</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
